--- a/datosNiveles.xlsx
+++ b/datosNiveles.xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4CA16F-938E-473B-81CC-FD9E9E53813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E6C76C-C4FE-4BD2-9836-D5B7630201D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="394">
   <si>
     <t>ID</t>
   </si>
@@ -98,39 +85,84 @@
     <t>Num errores por tiempo excedido</t>
   </si>
   <si>
+    <t>% Aciertos</t>
+  </si>
+  <si>
+    <t>% Mal</t>
+  </si>
+  <si>
     <t>15:04:04.517</t>
   </si>
   <si>
     <t>15:20:46.000</t>
   </si>
   <si>
+    <t>78.57142857142857</t>
+  </si>
+  <si>
+    <t>21.42857142857143</t>
+  </si>
+  <si>
     <t>14:15:08.014</t>
   </si>
   <si>
     <t>14:18:26.124</t>
   </si>
   <si>
+    <t>100.0</t>
+  </si>
+  <si>
+    <t>0.0</t>
+  </si>
+  <si>
     <t>14:33:17.624</t>
   </si>
   <si>
     <t>14:41:08.214</t>
   </si>
   <si>
+    <t>77.77777777777777</t>
+  </si>
+  <si>
+    <t>22.22222222222223</t>
+  </si>
+  <si>
     <t>14:41:36.785</t>
   </si>
   <si>
+    <t>0 planificado</t>
+  </si>
+  <si>
     <t>14:22:08.352</t>
   </si>
   <si>
     <t>14:33:47.295</t>
   </si>
   <si>
+    <t>80.0</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
     <t>14:41:54.930</t>
   </si>
   <si>
+    <t>90.0</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
     <t>14:45:59.368</t>
   </si>
   <si>
+    <t>83.33333333333333</t>
+  </si>
+  <si>
+    <t>16.66666666666667</t>
+  </si>
+  <si>
     <t>14:13:54.844</t>
   </si>
   <si>
@@ -158,6 +190,12 @@
     <t>14:33:28.259</t>
   </si>
   <si>
+    <t>75.0</t>
+  </si>
+  <si>
+    <t>25.0</t>
+  </si>
+  <si>
     <t>14:15:31.568</t>
   </si>
   <si>
@@ -170,6 +208,12 @@
     <t>14:40:03.212</t>
   </si>
   <si>
+    <t>85.71428571428571</t>
+  </si>
+  <si>
+    <t>14.285714285714292</t>
+  </si>
+  <si>
     <t>15:03:20.042</t>
   </si>
   <si>
@@ -185,6 +229,9 @@
     <t>15:40:07.396</t>
   </si>
   <si>
+    <t>50.0</t>
+  </si>
+  <si>
     <t>15:42:48.934</t>
   </si>
   <si>
@@ -221,6 +268,12 @@
     <t>14:40:03.021</t>
   </si>
   <si>
+    <t>94.44444444444444</t>
+  </si>
+  <si>
+    <t>5.555555555555557</t>
+  </si>
+  <si>
     <t>14:45:28.196</t>
   </si>
   <si>
@@ -233,6 +286,12 @@
     <t>14:31:57.052</t>
   </si>
   <si>
+    <t>88.88888888888889</t>
+  </si>
+  <si>
+    <t>11.111111111111114</t>
+  </si>
+  <si>
     <t>14:37:24.618</t>
   </si>
   <si>
@@ -248,6 +307,12 @@
     <t>14:55:21.747</t>
   </si>
   <si>
+    <t>76.47058823529412</t>
+  </si>
+  <si>
+    <t>23.529411764705884</t>
+  </si>
+  <si>
     <t>14:56:41.369</t>
   </si>
   <si>
@@ -260,12 +325,24 @@
     <t>15:12:14.966</t>
   </si>
   <si>
+    <t>60.0</t>
+  </si>
+  <si>
+    <t>40.0</t>
+  </si>
+  <si>
     <t>15:06:50.654</t>
   </si>
   <si>
     <t>15:12:14.783</t>
   </si>
   <si>
+    <t>87.5</t>
+  </si>
+  <si>
+    <t>12.5</t>
+  </si>
+  <si>
     <t>15:19:02.477</t>
   </si>
   <si>
@@ -281,6 +358,12 @@
     <t>14:43:21.606</t>
   </si>
   <si>
+    <t>76.92307692307692</t>
+  </si>
+  <si>
+    <t>23.07692307692308</t>
+  </si>
+  <si>
     <t>14:48:20.692</t>
   </si>
   <si>
@@ -317,6 +400,12 @@
     <t>15:51:25.871</t>
   </si>
   <si>
+    <t>90.47619047619048</t>
+  </si>
+  <si>
+    <t>9.523809523809518</t>
+  </si>
+  <si>
     <t>15:05:45.125</t>
   </si>
   <si>
@@ -326,9 +415,21 @@
     <t>15:21:30.015</t>
   </si>
   <si>
+    <t>86.66666666666667</t>
+  </si>
+  <si>
+    <t>13.333333333333329</t>
+  </si>
+  <si>
     <t>15:51:06.616</t>
   </si>
   <si>
+    <t>88.46153846153847</t>
+  </si>
+  <si>
+    <t>11.538461538461533</t>
+  </si>
+  <si>
     <t>15:51:06.619</t>
   </si>
   <si>
@@ -350,9 +451,21 @@
     <t>15:07:16.598</t>
   </si>
   <si>
+    <t>72.72727272727273</t>
+  </si>
+  <si>
+    <t>27.272727272727266</t>
+  </si>
+  <si>
     <t>15:53:03.221</t>
   </si>
   <si>
+    <t>93.93939393939394</t>
+  </si>
+  <si>
+    <t>6.060606060606062</t>
+  </si>
+  <si>
     <t>14:22:05.338</t>
   </si>
   <si>
@@ -377,6 +490,12 @@
     <t>15:19:31.478</t>
   </si>
   <si>
+    <t>73.6842105263158</t>
+  </si>
+  <si>
+    <t>26.315789473684205</t>
+  </si>
+  <si>
     <t>15:35:05.464</t>
   </si>
   <si>
@@ -389,6 +508,12 @@
     <t>15:13:30.278</t>
   </si>
   <si>
+    <t>90.9090909090909</t>
+  </si>
+  <si>
+    <t>9.090909090909093</t>
+  </si>
+  <si>
     <t>15:21:05.316</t>
   </si>
   <si>
@@ -407,6 +532,12 @@
     <t>15:42:14.394</t>
   </si>
   <si>
+    <t>79.16666666666667</t>
+  </si>
+  <si>
+    <t>20.83333333333333</t>
+  </si>
+  <si>
     <t>14:57:14.600</t>
   </si>
   <si>
@@ -425,6 +556,12 @@
     <t>15:37:20.923</t>
   </si>
   <si>
+    <t>71.42857142857143</t>
+  </si>
+  <si>
+    <t>28.57142857142857</t>
+  </si>
+  <si>
     <t>15:40:59.178</t>
   </si>
   <si>
@@ -449,18 +586,36 @@
     <t>15:42:01.441</t>
   </si>
   <si>
+    <t>66.66666666666667</t>
+  </si>
+  <si>
+    <t>33.33333333333333</t>
+  </si>
+  <si>
     <t>15:44:04.289</t>
   </si>
   <si>
     <t>15:53:09.504</t>
   </si>
   <si>
+    <t>54.54545454545455</t>
+  </si>
+  <si>
+    <t>45.45454545454545</t>
+  </si>
+  <si>
     <t>14:19:54.532</t>
   </si>
   <si>
     <t>14:50:35.180</t>
   </si>
   <si>
+    <t>86.36363636363636</t>
+  </si>
+  <si>
+    <t>13.63636363636364</t>
+  </si>
+  <si>
     <t>14:55:04.984</t>
   </si>
   <si>
@@ -488,6 +643,12 @@
     <t>15:35:37.780</t>
   </si>
   <si>
+    <t>72.5</t>
+  </si>
+  <si>
+    <t>27.5</t>
+  </si>
+  <si>
     <t>15:37:20.925</t>
   </si>
   <si>
@@ -512,12 +673,24 @@
     <t>15:53:16.524</t>
   </si>
   <si>
+    <t>81.25</t>
+  </si>
+  <si>
+    <t>18.75</t>
+  </si>
+  <si>
     <t>14:21:40.892</t>
   </si>
   <si>
     <t>14:44:31.489</t>
   </si>
   <si>
+    <t>92.3076923076923</t>
+  </si>
+  <si>
+    <t>7.692307692307693</t>
+  </si>
+  <si>
     <t>14:53:52.881</t>
   </si>
   <si>
@@ -710,6 +883,12 @@
     <t>15:32:58.880</t>
   </si>
   <si>
+    <t>93.33333333333333</t>
+  </si>
+  <si>
+    <t>6.666666666666671</t>
+  </si>
+  <si>
     <t>15:43:28.720</t>
   </si>
   <si>
@@ -737,9 +916,21 @@
     <t>15:05:24.859</t>
   </si>
   <si>
+    <t>35.714285714285715</t>
+  </si>
+  <si>
+    <t>64.28571428571428</t>
+  </si>
+  <si>
     <t>15:36:54.356</t>
   </si>
   <si>
+    <t>61.111111111111114</t>
+  </si>
+  <si>
+    <t>38.888888888888886</t>
+  </si>
+  <si>
     <t>16:00:54.514</t>
   </si>
   <si>
@@ -770,18 +961,36 @@
     <t>14:45:57.823</t>
   </si>
   <si>
+    <t>69.56521739130434</t>
+  </si>
+  <si>
+    <t>30.434782608695656</t>
+  </si>
+  <si>
     <t>14:50:19.392</t>
   </si>
   <si>
     <t>15:22:37.565</t>
   </si>
   <si>
+    <t>93.54838709677419</t>
+  </si>
+  <si>
+    <t>6.451612903225808</t>
+  </si>
+  <si>
     <t>16:50:34.650</t>
   </si>
   <si>
     <t>17:12:38.100</t>
   </si>
   <si>
+    <t>51.61290322580645</t>
+  </si>
+  <si>
+    <t>48.38709677419355</t>
+  </si>
+  <si>
     <t>17:16:54.856</t>
   </si>
   <si>
@@ -815,6 +1024,12 @@
     <t>14:32:00.853</t>
   </si>
   <si>
+    <t>88.23529411764706</t>
+  </si>
+  <si>
+    <t>11.764705882352942</t>
+  </si>
+  <si>
     <t>14:21:08.325</t>
   </si>
   <si>
@@ -908,6 +1123,12 @@
     <t>14:38:49.040</t>
   </si>
   <si>
+    <t>75.86206896551724</t>
+  </si>
+  <si>
+    <t>24.13793103448276</t>
+  </si>
+  <si>
     <t>14:42:45.561</t>
   </si>
   <si>
@@ -935,12 +1156,24 @@
     <t>14:58:20.061</t>
   </si>
   <si>
+    <t>76.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
     <t>15:19:07.753</t>
   </si>
   <si>
     <t>15:42:49.649</t>
   </si>
   <si>
+    <t>93.75</t>
+  </si>
+  <si>
+    <t>6.25</t>
+  </si>
+  <si>
     <t>15:49:09.643</t>
   </si>
   <si>
@@ -953,10 +1186,22 @@
     <t>16:12:56.886</t>
   </si>
   <si>
+    <t>64.28571428571429</t>
+  </si>
+  <si>
+    <t>35.71428571428571</t>
+  </si>
+  <si>
     <t>16:16:52.592</t>
   </si>
   <si>
     <t>16:30:37.739</t>
+  </si>
+  <si>
+    <t>82.3529411764706</t>
+  </si>
+  <si>
+    <t>17.647058823529406</t>
   </si>
 </sst>
 </file>
@@ -1076,30 +1321,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{EDB1CCCA-E24E-4260-8706-2A035DDE2F94}" name="Tabla2" displayName="Tabla2" ref="A1:U213" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
-  <autoFilter ref="A1:U213" xr:uid="{EDB1CCCA-E24E-4260-8706-2A035DDE2F94}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{66EE3AF2-96D5-4AAF-9CCA-C98ED5082220}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{E82EFA99-6924-4532-B0C0-B497F6ABCD3D}" name="Sesion"/>
-    <tableColumn id="3" xr3:uid="{A803E008-9A31-47C7-8043-5258AD28BCBC}" name="Nivel"/>
-    <tableColumn id="4" xr3:uid="{2163A303-D224-4FEC-9C6B-3247E970F404}" name="Num intentos"/>
-    <tableColumn id="5" xr3:uid="{8CD86A70-C1E1-41BF-B922-6FDF07A6DDF8}" name="Tiempo inicio"/>
-    <tableColumn id="6" xr3:uid="{6A4D71F1-4D2E-4913-95A8-ADA6E53CA8AA}" name="Tiempo final"/>
-    <tableColumn id="7" xr3:uid="{C912BD31-F4DC-4F06-AB90-EA5A285CAC8C}" name="Tiempo duracion"/>
-    <tableColumn id="8" xr3:uid="{7010A196-88D8-45A9-8AF0-8C6A2104E2E7}" name="Completado"/>
-    <tableColumn id="9" xr3:uid="{47C5B22E-100D-4F29-B6EC-021CF0F3D82C}" name="Pasos planificados"/>
-    <tableColumn id="10" xr3:uid="{00959E54-3934-46CA-AFA8-8649AB317B04}" name="Pasos ejecutados"/>
-    <tableColumn id="11" xr3:uid="{E2040936-C704-494D-A028-16A5E29CDC98}" name="Errores ejecucion"/>
-    <tableColumn id="12" xr3:uid="{50156CD7-0E4D-4BDF-9D16-50B919FBB3B0}" name="Num dormir planificado"/>
-    <tableColumn id="13" xr3:uid="{12779829-821F-42BA-B47C-D07483B06AB6}" name="Correctos dormir"/>
-    <tableColumn id="14" xr3:uid="{0B4E3898-8CD9-4815-A1D4-05C6783B01EB}" name="Errores dormir"/>
-    <tableColumn id="15" xr3:uid="{01BE5ADD-428E-4ABC-8408-9F0B74A51615}" name="Num ubicacion planificado"/>
-    <tableColumn id="16" xr3:uid="{7CC6C0F1-AA40-4CC5-9BE1-6699EE298874}" name="Correctos ubicacion"/>
-    <tableColumn id="17" xr3:uid="{A8DC5282-89F3-40BF-AD00-EFB20BA5C723}" name="Errores ubicacion"/>
-    <tableColumn id="18" xr3:uid="{8412FA4D-FD51-4A76-8B86-B172B64416FF}" name="Paradas posibles"/>
-    <tableColumn id="19" xr3:uid="{223CC02A-F206-4226-9BD0-BD0F75587A83}" name="Paradas realizadas"/>
-    <tableColumn id="20" xr3:uid="{1197B8FD-5C04-4416-AF63-471290E9743A}" name="Errores parada por tiempo excedido"/>
-    <tableColumn id="21" xr3:uid="{37992760-4170-4407-ACAB-E5194A3F00DC}" name="Num errores por tiempo excedido"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D13D78F-AC41-4729-B506-72214316E2AA}" name="Tabla1" displayName="Tabla1" ref="A1:W213" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:W213" xr:uid="{1D13D78F-AC41-4729-B506-72214316E2AA}"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{26CFCA52-95FF-4CE8-9413-A359BC904B01}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{27CDD6F9-83DC-4309-93DE-636DA3E383A3}" name="Sesion"/>
+    <tableColumn id="3" xr3:uid="{62D8205C-B719-4533-AD4E-ADE2DA142383}" name="Nivel"/>
+    <tableColumn id="4" xr3:uid="{82A4ADDE-FD10-4937-B052-9100751AC7D6}" name="Num intentos"/>
+    <tableColumn id="5" xr3:uid="{099CDFF5-08D5-43E7-8439-FC172D112A78}" name="Tiempo inicio"/>
+    <tableColumn id="6" xr3:uid="{EFB2310C-166A-454B-A3B4-EB72D553758A}" name="Tiempo final"/>
+    <tableColumn id="7" xr3:uid="{43BA5940-1F7C-43D6-8748-22487C74F572}" name="Tiempo duracion"/>
+    <tableColumn id="8" xr3:uid="{FCB7D162-BDCB-41EF-8E4A-15170046CFBD}" name="Completado"/>
+    <tableColumn id="9" xr3:uid="{5DD594F7-83B1-434A-9492-13D62986C975}" name="Pasos planificados"/>
+    <tableColumn id="10" xr3:uid="{04905EBA-E70C-46C6-938A-644BE78E4D36}" name="Pasos ejecutados"/>
+    <tableColumn id="11" xr3:uid="{5711AD15-5BB2-4940-923B-4A11873DDFBB}" name="Errores ejecucion"/>
+    <tableColumn id="12" xr3:uid="{23789CF1-3A24-4198-9CFD-C307F2F4565F}" name="Num dormir planificado"/>
+    <tableColumn id="13" xr3:uid="{6FF8852B-7A6C-43B7-A997-2886AB761426}" name="Correctos dormir"/>
+    <tableColumn id="14" xr3:uid="{63FF2413-8DF0-4DF8-BFC4-B8315DC058A6}" name="Errores dormir"/>
+    <tableColumn id="15" xr3:uid="{32614C3D-4D8F-4D64-A064-DE002AA5AE9E}" name="Num ubicacion planificado"/>
+    <tableColumn id="16" xr3:uid="{A3DCE512-8C3C-4424-875C-6BEA9E124F46}" name="Correctos ubicacion"/>
+    <tableColumn id="17" xr3:uid="{B91823FC-4B75-4A5A-9055-A19B0718CA94}" name="Errores ubicacion"/>
+    <tableColumn id="18" xr3:uid="{6DC55D6B-3C33-4479-BB86-6D72EBB2F643}" name="Paradas posibles"/>
+    <tableColumn id="19" xr3:uid="{FA62A870-8138-4514-8858-D5CB0BF6CEF9}" name="Paradas realizadas"/>
+    <tableColumn id="20" xr3:uid="{0A99A1FB-99B9-40A8-A466-F0E00EE20FB8}" name="Errores parada por tiempo excedido"/>
+    <tableColumn id="21" xr3:uid="{B9051385-8170-4D8A-9FB5-1D2E8F3763C4}" name="Num errores por tiempo excedido"/>
+    <tableColumn id="22" xr3:uid="{40592BCC-DE52-47F8-9A7E-CE3700C4F089}" name="% Aciertos"/>
+    <tableColumn id="23" xr3:uid="{1403DEE8-738A-4588-9141-275C990F50F6}" name="% Mal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1390,7 +1637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U213"/>
+  <dimension ref="A1:W213"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
@@ -1410,9 +1657,10 @@
     <col min="19" max="19" width="18.21875" customWidth="1"/>
     <col min="20" max="20" width="32.88671875" customWidth="1"/>
     <col min="21" max="21" width="31.109375" customWidth="1"/>
+    <col min="22" max="23" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1476,8 +1724,14 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1491,10 +1745,10 @@
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2">
         <v>1001.4829999999999</v>
@@ -1541,8 +1795,14 @@
       <c r="U2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1556,10 +1816,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G3">
         <v>198.11</v>
@@ -1606,8 +1866,14 @@
       <c r="U3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V3" t="s">
+        <v>29</v>
+      </c>
+      <c r="W3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>10</v>
       </c>
@@ -1621,10 +1887,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G4">
         <v>891.5</v>
@@ -1671,8 +1937,14 @@
       <c r="U4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V4" t="s">
+        <v>29</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>10</v>
       </c>
@@ -1686,10 +1958,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G5">
         <v>470.59</v>
@@ -1736,8 +2008,14 @@
       <c r="U5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V5" t="s">
+        <v>33</v>
+      </c>
+      <c r="W5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>10</v>
       </c>
@@ -1751,10 +2029,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>28.571000000000002</v>
@@ -1801,8 +2079,14 @@
       <c r="U6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V6" t="s">
+        <v>36</v>
+      </c>
+      <c r="W6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>11</v>
       </c>
@@ -1816,10 +2100,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G7">
         <v>698.94299999999998</v>
@@ -1866,8 +2150,14 @@
       <c r="U7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V7" t="s">
+        <v>39</v>
+      </c>
+      <c r="W7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>11</v>
       </c>
@@ -1881,10 +2171,10 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="G8">
         <v>487.63499999999999</v>
@@ -1931,8 +2221,14 @@
       <c r="U8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V8" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>11</v>
       </c>
@@ -1946,10 +2242,10 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="G9">
         <v>244.43799999999999</v>
@@ -1996,8 +2292,14 @@
       <c r="U9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V9" t="s">
+        <v>45</v>
+      </c>
+      <c r="W9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>11</v>
       </c>
@@ -2011,10 +2313,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="G10">
         <v>377.255</v>
@@ -2061,8 +2363,14 @@
       <c r="U10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V10" t="s">
+        <v>33</v>
+      </c>
+      <c r="W10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>11</v>
       </c>
@@ -2076,10 +2384,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G11">
         <v>221.697</v>
@@ -2126,8 +2434,14 @@
       <c r="U11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V11" t="s">
+        <v>29</v>
+      </c>
+      <c r="W11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2141,10 +2455,10 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G12">
         <v>324.53300000000002</v>
@@ -2191,8 +2505,14 @@
       <c r="U12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V12" t="s">
+        <v>45</v>
+      </c>
+      <c r="W12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2206,10 +2526,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="F13" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G13">
         <v>3.0000000000000001E-3</v>
@@ -2256,8 +2576,14 @@
       <c r="U13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V13" t="s">
+        <v>36</v>
+      </c>
+      <c r="W13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2271,10 +2597,10 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="G14">
         <v>395.01100000000002</v>
@@ -2321,8 +2647,14 @@
       <c r="U14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V14" t="s">
+        <v>29</v>
+      </c>
+      <c r="W14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2336,10 +2668,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G15">
         <v>251.125</v>
@@ -2386,8 +2718,14 @@
       <c r="U15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V15" t="s">
+        <v>29</v>
+      </c>
+      <c r="W15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13</v>
       </c>
@@ -2401,10 +2739,10 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G16">
         <v>165.10400000000001</v>
@@ -2451,8 +2789,14 @@
       <c r="U16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V16" t="s">
+        <v>56</v>
+      </c>
+      <c r="W16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>13</v>
       </c>
@@ -2466,10 +2810,10 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>766.95100000000002</v>
@@ -2516,8 +2860,14 @@
       <c r="U17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V17" t="s">
+        <v>29</v>
+      </c>
+      <c r="W17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>13</v>
       </c>
@@ -2531,10 +2881,10 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G18">
         <v>412.25</v>
@@ -2581,8 +2931,14 @@
       <c r="U18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V18" t="s">
+        <v>29</v>
+      </c>
+      <c r="W18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>13</v>
       </c>
@@ -2596,10 +2952,10 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="G19">
         <v>292.44299999999998</v>
@@ -2646,8 +3002,14 @@
       <c r="U19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V19" t="s">
+        <v>62</v>
+      </c>
+      <c r="W19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>15</v>
       </c>
@@ -2661,10 +3023,10 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G20">
         <v>675.44</v>
@@ -2711,8 +3073,14 @@
       <c r="U20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V20" t="s">
+        <v>36</v>
+      </c>
+      <c r="W20" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>15</v>
       </c>
@@ -2726,10 +3094,10 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="G21">
         <v>331.98099999999999</v>
@@ -2776,8 +3144,14 @@
       <c r="U21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V21" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>16</v>
       </c>
@@ -2791,10 +3165,10 @@
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="G22">
         <v>625.00599999999997</v>
@@ -2841,8 +3215,14 @@
       <c r="U22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>16</v>
       </c>
@@ -2856,10 +3236,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G23">
         <v>161.53800000000001</v>
@@ -2906,8 +3286,14 @@
       <c r="U23">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V23" t="s">
+        <v>30</v>
+      </c>
+      <c r="W23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>16</v>
       </c>
@@ -2921,10 +3307,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G24">
         <v>191.298</v>
@@ -2971,8 +3357,14 @@
       <c r="U24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V24" t="s">
+        <v>29</v>
+      </c>
+      <c r="W24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>16</v>
       </c>
@@ -2986,10 +3378,10 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="G25">
         <v>590.29700000000003</v>
@@ -3036,8 +3428,14 @@
       <c r="U25">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V25" t="s">
+        <v>56</v>
+      </c>
+      <c r="W25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>16</v>
       </c>
@@ -3051,10 +3449,10 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G26">
         <v>425.238</v>
@@ -3101,8 +3499,14 @@
       <c r="U26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V26" t="s">
+        <v>29</v>
+      </c>
+      <c r="W26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>16</v>
       </c>
@@ -3116,10 +3520,10 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G27">
         <v>514.99199999999996</v>
@@ -3166,8 +3570,14 @@
       <c r="U27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V27" t="s">
+        <v>29</v>
+      </c>
+      <c r="W27" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>16</v>
       </c>
@@ -3181,10 +3591,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G28">
         <v>226.94800000000001</v>
@@ -3231,8 +3641,14 @@
       <c r="U28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V28" t="s">
+        <v>29</v>
+      </c>
+      <c r="W28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>16</v>
       </c>
@@ -3246,10 +3662,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="G29">
         <v>239.91</v>
@@ -3296,8 +3712,14 @@
       <c r="U29">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V29" t="s">
+        <v>29</v>
+      </c>
+      <c r="W29" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>16</v>
       </c>
@@ -3311,10 +3733,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="G30">
         <v>350.96199999999999</v>
@@ -3361,8 +3783,14 @@
       <c r="U30">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V30" t="s">
+        <v>29</v>
+      </c>
+      <c r="W30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>16</v>
       </c>
@@ -3376,10 +3804,10 @@
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G31">
         <v>445.16</v>
@@ -3426,8 +3854,14 @@
       <c r="U31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V31" t="s">
+        <v>56</v>
+      </c>
+      <c r="W31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>17</v>
       </c>
@@ -3441,10 +3875,10 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="G32">
         <v>1019.31</v>
@@ -3491,8 +3925,14 @@
       <c r="U32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V32" t="s">
+        <v>82</v>
+      </c>
+      <c r="W32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>17</v>
       </c>
@@ -3506,10 +3946,10 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="G33">
         <v>325.17500000000001</v>
@@ -3556,8 +3996,14 @@
       <c r="U33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V33" t="s">
+        <v>39</v>
+      </c>
+      <c r="W33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>17</v>
       </c>
@@ -3571,10 +4017,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="G34">
         <v>114.916</v>
@@ -3621,8 +4067,14 @@
       <c r="U34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V34" t="s">
+        <v>29</v>
+      </c>
+      <c r="W34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>17</v>
       </c>
@@ -3636,10 +4088,10 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G35">
         <v>1033.24</v>
@@ -3686,8 +4138,14 @@
       <c r="U35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V35" t="s">
+        <v>88</v>
+      </c>
+      <c r="W35" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>17</v>
       </c>
@@ -3701,10 +4159,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="G36">
         <v>327.56599999999997</v>
@@ -3751,8 +4209,14 @@
       <c r="U36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V36" t="s">
+        <v>29</v>
+      </c>
+      <c r="W36" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>17</v>
       </c>
@@ -3766,10 +4230,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F37" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G37">
         <v>391.79300000000001</v>
@@ -3816,8 +4280,14 @@
       <c r="U37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V37" t="s">
+        <v>29</v>
+      </c>
+      <c r="W37" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>17</v>
       </c>
@@ -3831,10 +4301,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F38" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="G38">
         <v>53.040999999999997</v>
@@ -3881,8 +4351,14 @@
       <c r="U38">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V38" t="s">
+        <v>36</v>
+      </c>
+      <c r="W38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>18</v>
       </c>
@@ -3896,10 +4372,10 @@
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="G39">
         <v>830.96100000000001</v>
@@ -3946,8 +4422,14 @@
       <c r="U39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V39" t="s">
+        <v>95</v>
+      </c>
+      <c r="W39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>18</v>
       </c>
@@ -3961,10 +4443,10 @@
         <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="F40" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="G40">
         <v>203.50800000000001</v>
@@ -4011,8 +4493,14 @@
       <c r="U40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V40" t="s">
+        <v>29</v>
+      </c>
+      <c r="W40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>18</v>
       </c>
@@ -4026,10 +4514,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="G41">
         <v>240.90199999999999</v>
@@ -4076,8 +4564,14 @@
       <c r="U41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V41" t="s">
+        <v>29</v>
+      </c>
+      <c r="W41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>18</v>
       </c>
@@ -4091,10 +4585,10 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="G42">
         <v>489.18700000000001</v>
@@ -4141,8 +4635,14 @@
       <c r="U42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V42" t="s">
+        <v>101</v>
+      </c>
+      <c r="W42" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>18</v>
       </c>
@@ -4156,10 +4656,10 @@
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="G43">
         <v>324.12900000000002</v>
@@ -4206,8 +4706,14 @@
       <c r="U43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V43" t="s">
+        <v>105</v>
+      </c>
+      <c r="W43" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>18</v>
       </c>
@@ -4221,10 +4727,10 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="F44" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="G44">
         <v>407.69400000000002</v>
@@ -4271,8 +4777,14 @@
       <c r="U44">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V44" t="s">
+        <v>45</v>
+      </c>
+      <c r="W44" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>18</v>
       </c>
@@ -4286,10 +4798,10 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="F45" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="G45">
         <v>1489.634</v>
@@ -4336,8 +4848,14 @@
       <c r="U45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V45" t="s">
+        <v>39</v>
+      </c>
+      <c r="W45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>18</v>
       </c>
@@ -4351,10 +4869,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F46" t="s">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="G46">
         <v>3.0000000000000001E-3</v>
@@ -4401,8 +4919,14 @@
       <c r="U46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>19</v>
       </c>
@@ -4416,10 +4940,10 @@
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="F47" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="G47">
         <v>1244.95</v>
@@ -4466,8 +4990,14 @@
       <c r="U47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V47" t="s">
+        <v>112</v>
+      </c>
+      <c r="W47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>19</v>
       </c>
@@ -4481,10 +5011,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="F48" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="G48">
         <v>299.08600000000001</v>
@@ -4531,8 +5061,14 @@
       <c r="U48">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V48" t="s">
+        <v>29</v>
+      </c>
+      <c r="W48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>19</v>
       </c>
@@ -4546,10 +5082,10 @@
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F49" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="G49">
         <v>150.49600000000001</v>
@@ -4596,8 +5132,14 @@
       <c r="U49">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V49" t="s">
+        <v>29</v>
+      </c>
+      <c r="W49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>19</v>
       </c>
@@ -4611,10 +5153,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="F50" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="G50">
         <v>337.06</v>
@@ -4661,8 +5203,14 @@
       <c r="U50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V50" t="s">
+        <v>29</v>
+      </c>
+      <c r="W50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>19</v>
       </c>
@@ -4676,10 +5224,10 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="G51">
         <v>344.19799999999998</v>
@@ -4726,8 +5274,14 @@
       <c r="U51">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V51" t="s">
+        <v>29</v>
+      </c>
+      <c r="W51" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>19</v>
       </c>
@@ -4741,10 +5295,10 @@
         <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="F52" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="G52">
         <v>379.60599999999999</v>
@@ -4791,8 +5345,14 @@
       <c r="U52">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V52" t="s">
+        <v>62</v>
+      </c>
+      <c r="W52" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1</v>
       </c>
@@ -4806,10 +5366,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="F53" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="G53">
         <v>430.90499999999997</v>
@@ -4856,8 +5416,14 @@
       <c r="U53">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V53" t="s">
+        <v>36</v>
+      </c>
+      <c r="W53" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>21</v>
       </c>
@@ -4871,10 +5437,10 @@
         <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="F54" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="G54">
         <v>784.26300000000003</v>
@@ -4921,8 +5487,14 @@
       <c r="U54">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V54" t="s">
+        <v>29</v>
+      </c>
+      <c r="W54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>21</v>
       </c>
@@ -4936,10 +5508,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="F55" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="G55">
         <v>239.89599999999999</v>
@@ -4986,8 +5558,14 @@
       <c r="U55">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V55" t="s">
+        <v>56</v>
+      </c>
+      <c r="W55" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>21</v>
       </c>
@@ -5001,10 +5579,10 @@
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="F56" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="G56">
         <v>546.42399999999998</v>
@@ -5051,8 +5629,14 @@
       <c r="U56">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V56" t="s">
+        <v>126</v>
+      </c>
+      <c r="W56" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>21</v>
       </c>
@@ -5066,10 +5650,10 @@
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>94</v>
+        <v>128</v>
       </c>
       <c r="F57" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="G57">
         <v>459.43299999999999</v>
@@ -5116,8 +5700,14 @@
       <c r="U57">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V57" t="s">
+        <v>29</v>
+      </c>
+      <c r="W57" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>21</v>
       </c>
@@ -5131,10 +5721,10 @@
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="F58" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="G58">
         <v>485.45699999999999</v>
@@ -5181,8 +5771,14 @@
       <c r="U58">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V58" t="s">
+        <v>131</v>
+      </c>
+      <c r="W58" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>21</v>
       </c>
@@ -5196,10 +5792,10 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F59" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="G59">
         <v>1776.6010000000001</v>
@@ -5246,8 +5842,14 @@
       <c r="U59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V59" t="s">
+        <v>134</v>
+      </c>
+      <c r="W59" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>21</v>
       </c>
@@ -5261,10 +5863,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>97</v>
+        <v>133</v>
       </c>
       <c r="F60" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="G60">
         <v>3.0000000000000001E-3</v>
@@ -5311,8 +5913,14 @@
       <c r="U60">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V60" t="s">
+        <v>36</v>
+      </c>
+      <c r="W60" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>22</v>
       </c>
@@ -5326,10 +5934,10 @@
         <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="F61" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="G61">
         <v>321.52800000000002</v>
@@ -5376,8 +5984,14 @@
       <c r="U61">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V61" t="s">
+        <v>36</v>
+      </c>
+      <c r="W61" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>22</v>
       </c>
@@ -5391,10 +6005,10 @@
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="F62" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="G62">
         <v>1034.588</v>
@@ -5441,8 +6055,14 @@
       <c r="U62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V62" t="s">
+        <v>29</v>
+      </c>
+      <c r="W62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>22</v>
       </c>
@@ -5456,10 +6076,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="F63" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="G63">
         <v>283.024</v>
@@ -5506,8 +6126,14 @@
       <c r="U63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V63" t="s">
+        <v>88</v>
+      </c>
+      <c r="W63" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>22</v>
       </c>
@@ -5521,10 +6147,10 @@
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="F64" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="G64">
         <v>465.21699999999998</v>
@@ -5571,8 +6197,14 @@
       <c r="U64">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V64" t="s">
+        <v>143</v>
+      </c>
+      <c r="W64" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>22</v>
       </c>
@@ -5586,10 +6218,10 @@
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="F65" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="G65">
         <v>2746.623</v>
@@ -5636,8 +6268,14 @@
       <c r="U65">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V65" t="s">
+        <v>146</v>
+      </c>
+      <c r="W65" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>23</v>
       </c>
@@ -5651,10 +6289,10 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="F66" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="G66">
         <v>1745.9690000000001</v>
@@ -5701,8 +6339,14 @@
       <c r="U66">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V66" t="s">
+        <v>25</v>
+      </c>
+      <c r="W66" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>23</v>
       </c>
@@ -5716,10 +6360,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="F67" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="G67">
         <v>136.61600000000001</v>
@@ -5766,8 +6410,14 @@
       <c r="U67">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V67" t="s">
+        <v>36</v>
+      </c>
+      <c r="W67" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>24</v>
       </c>
@@ -5781,10 +6431,10 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="F68" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="G68">
         <v>539.26599999999996</v>
@@ -5831,8 +6481,14 @@
       <c r="U68">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V68" t="s">
+        <v>36</v>
+      </c>
+      <c r="W68" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>24</v>
       </c>
@@ -5846,10 +6502,10 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="F69" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="G69">
         <v>596.93200000000002</v>
@@ -5896,8 +6552,14 @@
       <c r="U69">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V69" t="s">
+        <v>69</v>
+      </c>
+      <c r="W69" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>24</v>
       </c>
@@ -5911,10 +6573,10 @@
         <v>5</v>
       </c>
       <c r="E70" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="F70" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="G70">
         <v>1086.9169999999999</v>
@@ -5961,8 +6623,14 @@
       <c r="U70">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V70" t="s">
+        <v>156</v>
+      </c>
+      <c r="W70" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>24</v>
       </c>
@@ -5976,10 +6644,10 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="F71" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="G71">
         <v>933.98599999999999</v>
@@ -6026,8 +6694,14 @@
       <c r="U71">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V71" t="s">
+        <v>56</v>
+      </c>
+      <c r="W71" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>24</v>
       </c>
@@ -6041,10 +6715,10 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="F72" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="G72">
         <v>955.89599999999996</v>
@@ -6091,8 +6765,14 @@
       <c r="U72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V72" t="s">
+        <v>45</v>
+      </c>
+      <c r="W72" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>25</v>
       </c>
@@ -6106,10 +6786,10 @@
         <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="F73" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="G73">
         <v>1026.5830000000001</v>
@@ -6156,8 +6836,14 @@
       <c r="U73">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V73" t="s">
+        <v>162</v>
+      </c>
+      <c r="W73" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>25</v>
       </c>
@@ -6171,10 +6857,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="F74" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="G74">
         <v>455.03800000000001</v>
@@ -6221,8 +6907,14 @@
       <c r="U74">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V74" t="s">
+        <v>29</v>
+      </c>
+      <c r="W74" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>25</v>
       </c>
@@ -6236,10 +6928,10 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>118</v>
+        <v>164</v>
       </c>
       <c r="F75" t="s">
-        <v>119</v>
+        <v>165</v>
       </c>
       <c r="G75">
         <v>113.578</v>
@@ -6286,8 +6978,14 @@
       <c r="U75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V75" t="s">
+        <v>29</v>
+      </c>
+      <c r="W75" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>25</v>
       </c>
@@ -6301,10 +6999,10 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="F76" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="G76">
         <v>340.90100000000001</v>
@@ -6351,8 +7049,14 @@
       <c r="U76">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V76" t="s">
+        <v>29</v>
+      </c>
+      <c r="W76" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>25</v>
       </c>
@@ -6366,10 +7070,10 @@
         <v>6</v>
       </c>
       <c r="E77" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="F77" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="G77">
         <v>1365.6410000000001</v>
@@ -6416,8 +7120,14 @@
       <c r="U77">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V77" t="s">
+        <v>82</v>
+      </c>
+      <c r="W77" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>25</v>
       </c>
@@ -6431,10 +7141,10 @@
         <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="F78" t="s">
-        <v>123</v>
+        <v>169</v>
       </c>
       <c r="G78">
         <v>982.15499999999997</v>
@@ -6481,8 +7191,14 @@
       <c r="U78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V78" t="s">
+        <v>170</v>
+      </c>
+      <c r="W78" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>26</v>
       </c>
@@ -6496,10 +7212,10 @@
         <v>6</v>
       </c>
       <c r="E79" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="F79" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="G79">
         <v>1539.473</v>
@@ -6546,8 +7262,14 @@
       <c r="U79">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V79" t="s">
+        <v>29</v>
+      </c>
+      <c r="W79" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>26</v>
       </c>
@@ -6561,10 +7283,10 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>125</v>
+        <v>173</v>
       </c>
       <c r="F80" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
       <c r="G80">
         <v>182.26300000000001</v>
@@ -6611,8 +7333,14 @@
       <c r="U80">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V80" t="s">
+        <v>36</v>
+      </c>
+      <c r="W80" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>26</v>
       </c>
@@ -6626,10 +7354,10 @@
         <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="F81" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="G81">
         <v>577.74199999999996</v>
@@ -6676,8 +7404,14 @@
       <c r="U81">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V81" t="s">
+        <v>62</v>
+      </c>
+      <c r="W81" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>26</v>
       </c>
@@ -6691,10 +7425,10 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="F82" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="G82">
         <v>1772.241</v>
@@ -6741,8 +7475,14 @@
       <c r="U82">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V82" t="s">
+        <v>178</v>
+      </c>
+      <c r="W82" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>26</v>
       </c>
@@ -6756,10 +7496,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="F83" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="G83">
         <v>218.255</v>
@@ -6806,8 +7546,14 @@
       <c r="U83">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V83" t="s">
+        <v>36</v>
+      </c>
+      <c r="W83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>27</v>
       </c>
@@ -6821,10 +7567,10 @@
         <v>5</v>
       </c>
       <c r="E84" t="s">
-        <v>131</v>
+        <v>181</v>
       </c>
       <c r="F84" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="G84">
         <v>847.82100000000003</v>
@@ -6871,8 +7617,14 @@
       <c r="U84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V84" t="s">
+        <v>101</v>
+      </c>
+      <c r="W84" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>27</v>
       </c>
@@ -6886,10 +7638,10 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="F85" t="s">
-        <v>133</v>
+        <v>183</v>
       </c>
       <c r="G85">
         <v>76.603999999999999</v>
@@ -6936,8 +7688,14 @@
       <c r="U85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V85" t="s">
+        <v>36</v>
+      </c>
+      <c r="W85" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>27</v>
       </c>
@@ -6951,10 +7709,10 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="F86" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="G86">
         <v>293.68299999999999</v>
@@ -7001,8 +7759,14 @@
       <c r="U86">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V86" t="s">
+        <v>29</v>
+      </c>
+      <c r="W86" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>27</v>
       </c>
@@ -7016,10 +7780,10 @@
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="F87" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="G87">
         <v>1589.087</v>
@@ -7066,8 +7830,14 @@
       <c r="U87">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V87" t="s">
+        <v>29</v>
+      </c>
+      <c r="W87" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>27</v>
       </c>
@@ -7081,10 +7851,10 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="F88" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="G88">
         <v>188.63200000000001</v>
@@ -7131,8 +7901,14 @@
       <c r="U88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V88" t="s">
+        <v>188</v>
+      </c>
+      <c r="W88" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>27</v>
       </c>
@@ -7146,10 +7922,10 @@
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="F89" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G89">
         <v>122.848</v>
@@ -7196,8 +7972,14 @@
       <c r="U89">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V89" t="s">
+        <v>36</v>
+      </c>
+      <c r="W89" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>27</v>
       </c>
@@ -7211,10 +7993,10 @@
         <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="F90" t="s">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="G90">
         <v>545.21500000000003</v>
@@ -7261,8 +8043,14 @@
       <c r="U90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V90" t="s">
+        <v>192</v>
+      </c>
+      <c r="W90" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>2</v>
       </c>
@@ -7276,10 +8064,10 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="F91" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="G91">
         <v>1840.6479999999999</v>
@@ -7326,8 +8114,14 @@
       <c r="U91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V91" t="s">
+        <v>196</v>
+      </c>
+      <c r="W91" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>2</v>
       </c>
@@ -7341,10 +8135,10 @@
         <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="F92" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="G92">
         <v>269.80399999999997</v>
@@ -7391,8 +8185,14 @@
       <c r="U92">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V92" t="s">
+        <v>29</v>
+      </c>
+      <c r="W92" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>30</v>
       </c>
@@ -7406,10 +8206,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="F93" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="G93">
         <v>387.76600000000002</v>
@@ -7456,8 +8256,14 @@
       <c r="U93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V93" t="s">
+        <v>29</v>
+      </c>
+      <c r="W93" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>30</v>
       </c>
@@ -7471,10 +8277,10 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="F94" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="G94">
         <v>269.32299999999998</v>
@@ -7521,8 +8327,14 @@
       <c r="U94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V94" t="s">
+        <v>29</v>
+      </c>
+      <c r="W94" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>30</v>
       </c>
@@ -7536,10 +8348,10 @@
         <v>6</v>
       </c>
       <c r="E95" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
       <c r="F95" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
       <c r="G95">
         <v>1126.18</v>
@@ -7586,8 +8398,14 @@
       <c r="U95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V95" t="s">
+        <v>178</v>
+      </c>
+      <c r="W95" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>30</v>
       </c>
@@ -7601,10 +8419,10 @@
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="F96" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="G96">
         <v>327.07600000000002</v>
@@ -7651,8 +8469,14 @@
       <c r="U96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V96" t="s">
+        <v>39</v>
+      </c>
+      <c r="W96" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>30</v>
       </c>
@@ -7666,10 +8490,10 @@
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="F97" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="G97">
         <v>243.67</v>
@@ -7716,8 +8540,14 @@
       <c r="U97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V97" t="s">
+        <v>29</v>
+      </c>
+      <c r="W97" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>30</v>
       </c>
@@ -7731,10 +8561,10 @@
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="F98" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="G98">
         <v>1501.88</v>
@@ -7781,8 +8611,14 @@
       <c r="U98">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V98" t="s">
+        <v>207</v>
+      </c>
+      <c r="W98" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>30</v>
       </c>
@@ -7796,10 +8632,10 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="G99">
         <v>103.145</v>
@@ -7846,8 +8682,14 @@
       <c r="U99">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V99" t="s">
+        <v>36</v>
+      </c>
+      <c r="W99" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>30</v>
       </c>
@@ -7861,10 +8703,10 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="F100" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="G100">
         <v>307.60000000000002</v>
@@ -7911,8 +8753,14 @@
       <c r="U100">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V100" t="s">
+        <v>39</v>
+      </c>
+      <c r="W100" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>31</v>
       </c>
@@ -7926,10 +8774,10 @@
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="F101" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="G101">
         <v>626.35299999999995</v>
@@ -7976,8 +8824,14 @@
       <c r="U101">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V101" t="s">
+        <v>29</v>
+      </c>
+      <c r="W101" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>31</v>
       </c>
@@ -7991,10 +8845,10 @@
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="F102" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="G102">
         <v>1181.2190000000001</v>
@@ -8041,8 +8895,14 @@
       <c r="U102">
         <v>3</v>
       </c>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V102" t="s">
+        <v>88</v>
+      </c>
+      <c r="W102" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>31</v>
       </c>
@@ -8056,10 +8916,10 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="F103" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="G103">
         <v>349.72500000000002</v>
@@ -8106,8 +8966,14 @@
       <c r="U103">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V103" t="s">
+        <v>29</v>
+      </c>
+      <c r="W103" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>31</v>
       </c>
@@ -8121,10 +8987,10 @@
         <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="F104" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="G104">
         <v>2901.125</v>
@@ -8171,8 +9037,14 @@
       <c r="U104">
         <v>3</v>
       </c>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V104" t="s">
+        <v>217</v>
+      </c>
+      <c r="W104" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>32</v>
       </c>
@@ -8186,10 +9058,10 @@
         <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>159</v>
+        <v>219</v>
       </c>
       <c r="F105" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="G105">
         <v>1370.597</v>
@@ -8236,8 +9108,14 @@
       <c r="U105">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V105" t="s">
+        <v>221</v>
+      </c>
+      <c r="W105" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>32</v>
       </c>
@@ -8251,10 +9129,10 @@
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="F106" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="G106">
         <v>561.39200000000005</v>
@@ -8301,8 +9179,14 @@
       <c r="U106">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V106" t="s">
+        <v>131</v>
+      </c>
+      <c r="W106" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>32</v>
       </c>
@@ -8316,10 +9200,10 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="F107" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="G107">
         <v>346.435</v>
@@ -8366,8 +9250,14 @@
       <c r="U107">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V107" t="s">
+        <v>29</v>
+      </c>
+      <c r="W107" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>32</v>
       </c>
@@ -8381,10 +9271,10 @@
         <v>2</v>
       </c>
       <c r="E108" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="F108" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="G108">
         <v>318.33100000000002</v>
@@ -8431,8 +9321,14 @@
       <c r="U108">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V108" t="s">
+        <v>56</v>
+      </c>
+      <c r="W108" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>32</v>
       </c>
@@ -8446,10 +9342,10 @@
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="F109" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="G109">
         <v>116.30200000000001</v>
@@ -8496,8 +9392,14 @@
       <c r="U109">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V109" t="s">
+        <v>29</v>
+      </c>
+      <c r="W109" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>33</v>
       </c>
@@ -8511,10 +9413,10 @@
         <v>6</v>
       </c>
       <c r="E110" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="F110" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="G110">
         <v>1462.615</v>
@@ -8561,8 +9463,14 @@
       <c r="U110">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V110" t="s">
+        <v>36</v>
+      </c>
+      <c r="W110" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>34</v>
       </c>
@@ -8576,10 +9484,10 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="F111" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="G111">
         <v>254.846</v>
@@ -8626,8 +9534,14 @@
       <c r="U111">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V111" t="s">
+        <v>36</v>
+      </c>
+      <c r="W111" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>34</v>
       </c>
@@ -8641,10 +9555,10 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="F112" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="G112">
         <v>924.37099999999998</v>
@@ -8691,8 +9605,14 @@
       <c r="U112">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V112" t="s">
+        <v>36</v>
+      </c>
+      <c r="W112" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>34</v>
       </c>
@@ -8706,10 +9626,10 @@
         <v>3</v>
       </c>
       <c r="E113" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="F113" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="G113">
         <v>88.405000000000001</v>
@@ -8756,8 +9676,14 @@
       <c r="U113">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V113" t="s">
+        <v>36</v>
+      </c>
+      <c r="W113" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>35</v>
       </c>
@@ -8771,10 +9697,10 @@
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="F114" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="G114">
         <v>245.28100000000001</v>
@@ -8821,8 +9747,14 @@
       <c r="U114">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V114" t="s">
+        <v>36</v>
+      </c>
+      <c r="W114" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>35</v>
       </c>
@@ -8836,10 +9768,10 @@
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="F115" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="G115">
         <v>234.22200000000001</v>
@@ -8886,8 +9818,14 @@
       <c r="U115">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V115" t="s">
+        <v>36</v>
+      </c>
+      <c r="W115" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>35</v>
       </c>
@@ -8901,10 +9839,10 @@
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="F116" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="G116">
         <v>217.36199999999999</v>
@@ -8951,8 +9889,14 @@
       <c r="U116">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V116" t="s">
+        <v>36</v>
+      </c>
+      <c r="W116" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>35</v>
       </c>
@@ -8966,10 +9910,10 @@
         <v>6</v>
       </c>
       <c r="E117" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="F117" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="G117">
         <v>1188.2809999999999</v>
@@ -9016,8 +9960,14 @@
       <c r="U117">
         <v>4</v>
       </c>
-    </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V117" t="s">
+        <v>36</v>
+      </c>
+      <c r="W117" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>35</v>
       </c>
@@ -9031,10 +9981,10 @@
         <v>5</v>
       </c>
       <c r="E118" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="F118" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="G118">
         <v>974.44600000000003</v>
@@ -9081,8 +10031,14 @@
       <c r="U118">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V118" t="s">
+        <v>39</v>
+      </c>
+      <c r="W118" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>35</v>
       </c>
@@ -9096,10 +10052,10 @@
         <v>4</v>
       </c>
       <c r="E119" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="F119" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="G119">
         <v>934.26599999999996</v>
@@ -9146,8 +10102,14 @@
       <c r="U119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V119" t="s">
+        <v>88</v>
+      </c>
+      <c r="W119" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>35</v>
       </c>
@@ -9161,10 +10123,10 @@
         <v>3</v>
       </c>
       <c r="E120" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="F120" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="G120">
         <v>519.375</v>
@@ -9211,8 +10173,14 @@
       <c r="U120">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V120" t="s">
+        <v>178</v>
+      </c>
+      <c r="W120" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>35</v>
       </c>
@@ -9226,10 +10194,10 @@
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="F121" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="G121">
         <v>287.03899999999999</v>
@@ -9276,8 +10244,14 @@
       <c r="U121">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V121" t="s">
+        <v>56</v>
+      </c>
+      <c r="W121" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>35</v>
       </c>
@@ -9291,10 +10265,10 @@
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="F122" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="G122">
         <v>254.63399999999999</v>
@@ -9341,8 +10315,14 @@
       <c r="U122">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V122" t="s">
+        <v>29</v>
+      </c>
+      <c r="W122" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>35</v>
       </c>
@@ -9356,10 +10336,10 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="F123" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="G123">
         <v>151.352</v>
@@ -9406,8 +10386,14 @@
       <c r="U123">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V123" t="s">
+        <v>29</v>
+      </c>
+      <c r="W123" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>37</v>
       </c>
@@ -9421,10 +10407,10 @@
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="F124" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="G124">
         <v>802.04100000000005</v>
@@ -9471,8 +10457,14 @@
       <c r="U124">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V124" t="s">
+        <v>29</v>
+      </c>
+      <c r="W124" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="125" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>37</v>
       </c>
@@ -9486,10 +10478,10 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="F125" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="G125">
         <v>255.15600000000001</v>
@@ -9536,8 +10528,14 @@
       <c r="U125">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V125" t="s">
+        <v>188</v>
+      </c>
+      <c r="W125" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="126" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>37</v>
       </c>
@@ -9551,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="F126" t="s">
-        <v>187</v>
+        <v>249</v>
       </c>
       <c r="G126">
         <v>157.999</v>
@@ -9601,8 +10599,14 @@
       <c r="U126">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V126" t="s">
+        <v>29</v>
+      </c>
+      <c r="W126" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="127" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>37</v>
       </c>
@@ -9616,10 +10620,10 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>187</v>
+        <v>249</v>
       </c>
       <c r="F127" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="G127">
         <v>410.64400000000001</v>
@@ -9666,8 +10670,14 @@
       <c r="U127">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V127" t="s">
+        <v>188</v>
+      </c>
+      <c r="W127" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>37</v>
       </c>
@@ -9681,10 +10691,10 @@
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="F128" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="G128">
         <v>195.59299999999999</v>
@@ -9731,8 +10741,14 @@
       <c r="U128">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V128" t="s">
+        <v>101</v>
+      </c>
+      <c r="W128" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="129" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>37</v>
       </c>
@@ -9746,10 +10762,10 @@
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="F129" t="s">
-        <v>190</v>
+        <v>252</v>
       </c>
       <c r="G129">
         <v>146.059</v>
@@ -9796,8 +10812,14 @@
       <c r="U129">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V129" t="s">
+        <v>29</v>
+      </c>
+      <c r="W129" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="130" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>37</v>
       </c>
@@ -9811,10 +10833,10 @@
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="F130" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="G130">
         <v>416.86200000000002</v>
@@ -9861,8 +10883,14 @@
       <c r="U130">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V130" t="s">
+        <v>105</v>
+      </c>
+      <c r="W130" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="131" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>37</v>
       </c>
@@ -9876,10 +10904,10 @@
         <v>1</v>
       </c>
       <c r="E131" t="s">
-        <v>192</v>
+        <v>254</v>
       </c>
       <c r="F131" t="s">
-        <v>193</v>
+        <v>255</v>
       </c>
       <c r="G131">
         <v>281.108</v>
@@ -9926,8 +10954,14 @@
       <c r="U131">
         <v>2</v>
       </c>
-    </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V131" t="s">
+        <v>29</v>
+      </c>
+      <c r="W131" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>37</v>
       </c>
@@ -9941,10 +10975,10 @@
         <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>193</v>
+        <v>255</v>
       </c>
       <c r="F132" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="G132">
         <v>222.53200000000001</v>
@@ -9991,8 +11025,14 @@
       <c r="U132">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V132" t="s">
+        <v>29</v>
+      </c>
+      <c r="W132" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>37</v>
       </c>
@@ -10006,10 +11046,10 @@
         <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>194</v>
+        <v>256</v>
       </c>
       <c r="F133" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="G133">
         <v>207.91800000000001</v>
@@ -10056,8 +11096,14 @@
       <c r="U133">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V133" t="s">
+        <v>29</v>
+      </c>
+      <c r="W133" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>37</v>
       </c>
@@ -10071,10 +11117,10 @@
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>195</v>
+        <v>257</v>
       </c>
       <c r="F134" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="G134">
         <v>438.53899999999999</v>
@@ -10121,8 +11167,14 @@
       <c r="U134">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V134" t="s">
+        <v>29</v>
+      </c>
+      <c r="W134" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>3</v>
       </c>
@@ -10136,10 +11188,10 @@
         <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>197</v>
+        <v>259</v>
       </c>
       <c r="F135" t="s">
-        <v>198</v>
+        <v>260</v>
       </c>
       <c r="G135">
         <v>7.0000000000000001E-3</v>
@@ -10186,8 +11238,14 @@
       <c r="U135">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V135" t="s">
+        <v>36</v>
+      </c>
+      <c r="W135" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>3</v>
       </c>
@@ -10201,10 +11259,10 @@
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>199</v>
+        <v>261</v>
       </c>
       <c r="F136" t="s">
-        <v>200</v>
+        <v>262</v>
       </c>
       <c r="G136">
         <v>379.57499999999999</v>
@@ -10251,8 +11309,14 @@
       <c r="U136">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V136" t="s">
+        <v>36</v>
+      </c>
+      <c r="W136" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>41</v>
       </c>
@@ -10266,10 +11330,10 @@
         <v>2</v>
       </c>
       <c r="E137" t="s">
-        <v>201</v>
+        <v>263</v>
       </c>
       <c r="F137" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="G137">
         <v>361.988</v>
@@ -10316,8 +11380,14 @@
       <c r="U137">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V137" t="s">
+        <v>56</v>
+      </c>
+      <c r="W137" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>41</v>
       </c>
@@ -10331,10 +11401,10 @@
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="F138" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="G138">
         <v>293.10599999999999</v>
@@ -10381,8 +11451,14 @@
       <c r="U138">
         <v>1</v>
       </c>
-    </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V138" t="s">
+        <v>29</v>
+      </c>
+      <c r="W138" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>41</v>
       </c>
@@ -10396,10 +11472,10 @@
         <v>4</v>
       </c>
       <c r="E139" t="s">
-        <v>203</v>
+        <v>265</v>
       </c>
       <c r="F139" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
       <c r="G139">
         <v>530.96</v>
@@ -10446,8 +11522,14 @@
       <c r="U139">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V139" t="s">
+        <v>25</v>
+      </c>
+      <c r="W139" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>41</v>
       </c>
@@ -10461,10 +11543,10 @@
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>204</v>
+        <v>266</v>
       </c>
       <c r="F140" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="G140">
         <v>3.0000000000000001E-3</v>
@@ -10511,8 +11593,14 @@
       <c r="U140">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V140" t="s">
+        <v>36</v>
+      </c>
+      <c r="W140" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>42</v>
       </c>
@@ -10526,10 +11614,10 @@
         <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="F141" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="G141">
         <v>326.041</v>
@@ -10576,8 +11664,14 @@
       <c r="U141">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V141" t="s">
+        <v>36</v>
+      </c>
+      <c r="W141" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>42</v>
       </c>
@@ -10591,10 +11685,10 @@
         <v>3</v>
       </c>
       <c r="E142" t="s">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="F142" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="G142">
         <v>802.67700000000002</v>
@@ -10641,8 +11735,14 @@
       <c r="U142">
         <v>2</v>
       </c>
-    </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V142" t="s">
+        <v>36</v>
+      </c>
+      <c r="W142" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>42</v>
       </c>
@@ -10656,10 +11756,10 @@
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="F143" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="G143">
         <v>3.0000000000000001E-3</v>
@@ -10706,8 +11806,14 @@
       <c r="U143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V143" t="s">
+        <v>36</v>
+      </c>
+      <c r="W143" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>43</v>
       </c>
@@ -10721,10 +11827,10 @@
         <v>10</v>
       </c>
       <c r="E144" t="s">
-        <v>210</v>
+        <v>272</v>
       </c>
       <c r="F144" t="s">
-        <v>211</v>
+        <v>273</v>
       </c>
       <c r="G144">
         <v>1324.8530000000001</v>
@@ -10771,8 +11877,14 @@
       <c r="U144">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V144" t="s">
+        <v>88</v>
+      </c>
+      <c r="W144" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>43</v>
       </c>
@@ -10786,10 +11898,10 @@
         <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>212</v>
+        <v>274</v>
       </c>
       <c r="F145" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="G145">
         <v>718.51300000000003</v>
@@ -10836,8 +11948,14 @@
       <c r="U145">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V145" t="s">
+        <v>112</v>
+      </c>
+      <c r="W145" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>43</v>
       </c>
@@ -10851,10 +11969,10 @@
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>213</v>
+        <v>275</v>
       </c>
       <c r="F146" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="G146">
         <v>250.69399999999999</v>
@@ -10901,8 +12019,14 @@
       <c r="U146">
         <v>2</v>
       </c>
-    </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V146" t="s">
+        <v>45</v>
+      </c>
+      <c r="W146" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>43</v>
       </c>
@@ -10916,10 +12040,10 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>214</v>
+        <v>276</v>
       </c>
       <c r="F147" t="s">
-        <v>215</v>
+        <v>277</v>
       </c>
       <c r="G147">
         <v>276.25599999999997</v>
@@ -10966,8 +12090,14 @@
       <c r="U147">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V147" t="s">
+        <v>25</v>
+      </c>
+      <c r="W147" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>44</v>
       </c>
@@ -10981,10 +12111,10 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>216</v>
+        <v>278</v>
       </c>
       <c r="F148" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="G148">
         <v>213.15899999999999</v>
@@ -11031,8 +12161,14 @@
       <c r="U148">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V148" t="s">
+        <v>36</v>
+      </c>
+      <c r="W148" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>44</v>
       </c>
@@ -11046,10 +12182,10 @@
         <v>3</v>
       </c>
       <c r="E149" t="s">
-        <v>217</v>
+        <v>279</v>
       </c>
       <c r="F149" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="G149">
         <v>531.59</v>
@@ -11096,8 +12232,14 @@
       <c r="U149">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V149" t="s">
+        <v>36</v>
+      </c>
+      <c r="W149" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>45</v>
       </c>
@@ -11111,10 +12253,10 @@
         <v>4</v>
       </c>
       <c r="E150" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="F150" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="G150">
         <v>688.51300000000003</v>
@@ -11161,8 +12303,14 @@
       <c r="U150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V150" t="s">
+        <v>29</v>
+      </c>
+      <c r="W150" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>45</v>
       </c>
@@ -11176,10 +12324,10 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="F151" t="s">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="G151">
         <v>436.10700000000003</v>
@@ -11226,8 +12374,14 @@
       <c r="U151">
         <v>4</v>
       </c>
-    </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V151" t="s">
+        <v>30</v>
+      </c>
+      <c r="W151" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>45</v>
       </c>
@@ -11241,10 +12395,10 @@
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="F152" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="G152">
         <v>666.76099999999997</v>
@@ -11291,8 +12445,14 @@
       <c r="U152">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V152" t="s">
+        <v>62</v>
+      </c>
+      <c r="W152" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>45</v>
       </c>
@@ -11306,10 +12466,10 @@
         <v>4</v>
       </c>
       <c r="E153" t="s">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="F153" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="G153">
         <v>1686.739</v>
@@ -11356,8 +12516,14 @@
       <c r="U153">
         <v>6</v>
       </c>
-    </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V153" t="s">
+        <v>287</v>
+      </c>
+      <c r="W153" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>45</v>
       </c>
@@ -11371,10 +12537,10 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="F154" t="s">
-        <v>225</v>
+        <v>289</v>
       </c>
       <c r="G154">
         <v>629.84</v>
@@ -11421,8 +12587,14 @@
       <c r="U154">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V154" t="s">
+        <v>105</v>
+      </c>
+      <c r="W154" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>46</v>
       </c>
@@ -11436,10 +12608,10 @@
         <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>226</v>
+        <v>290</v>
       </c>
       <c r="F155" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="G155">
         <v>416.16300000000001</v>
@@ -11486,8 +12658,14 @@
       <c r="U155">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V155" t="s">
+        <v>36</v>
+      </c>
+      <c r="W155" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>46</v>
       </c>
@@ -11501,10 +12679,10 @@
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="F156" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="G156">
         <v>103.598</v>
@@ -11551,8 +12729,14 @@
       <c r="U156">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V156" t="s">
+        <v>36</v>
+      </c>
+      <c r="W156" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>46</v>
       </c>
@@ -11566,10 +12750,10 @@
         <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="F157" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="G157">
         <v>271.584</v>
@@ -11616,8 +12800,14 @@
       <c r="U157">
         <v>2</v>
       </c>
-    </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V157" t="s">
+        <v>56</v>
+      </c>
+      <c r="W157" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>47</v>
       </c>
@@ -11631,10 +12821,10 @@
         <v>3</v>
       </c>
       <c r="E158" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="F158" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="G158">
         <v>302.63200000000001</v>
@@ -11681,8 +12871,14 @@
       <c r="U158">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V158" t="s">
+        <v>29</v>
+      </c>
+      <c r="W158" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>47</v>
       </c>
@@ -11696,10 +12892,10 @@
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="F159" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="G159">
         <v>455.70600000000002</v>
@@ -11746,8 +12942,14 @@
       <c r="U159">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V159" t="s">
+        <v>298</v>
+      </c>
+      <c r="W159" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>47</v>
       </c>
@@ -11761,10 +12963,10 @@
         <v>15</v>
       </c>
       <c r="E160" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="F160" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="G160">
         <v>1889.4970000000001</v>
@@ -11811,8 +13013,14 @@
       <c r="U160">
         <v>7</v>
       </c>
-    </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V160" t="s">
+        <v>301</v>
+      </c>
+      <c r="W160" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>47</v>
       </c>
@@ -11826,10 +13034,10 @@
         <v>6</v>
       </c>
       <c r="E161" t="s">
-        <v>234</v>
+        <v>300</v>
       </c>
       <c r="F161" t="s">
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="G161">
         <v>1440.1579999999999</v>
@@ -11876,8 +13084,14 @@
       <c r="U161">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V161" t="s">
+        <v>36</v>
+      </c>
+      <c r="W161" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>48</v>
       </c>
@@ -11891,10 +13105,10 @@
         <v>3</v>
       </c>
       <c r="E162" t="s">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="F162" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="G162">
         <v>305.84699999999998</v>
@@ -11941,8 +13155,14 @@
       <c r="U162">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V162" t="s">
+        <v>29</v>
+      </c>
+      <c r="W162" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>48</v>
       </c>
@@ -11956,10 +13176,10 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="F163" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="G163">
         <v>281.69600000000003</v>
@@ -12006,8 +13226,14 @@
       <c r="U163">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V163" t="s">
+        <v>36</v>
+      </c>
+      <c r="W163" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>48</v>
       </c>
@@ -12021,10 +13247,10 @@
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>238</v>
+        <v>306</v>
       </c>
       <c r="F164" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="G164">
         <v>332</v>
@@ -12071,8 +13297,14 @@
       <c r="U164">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V164" t="s">
+        <v>36</v>
+      </c>
+      <c r="W164" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>48</v>
       </c>
@@ -12086,10 +13318,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="F165" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="G165">
         <v>242.14500000000001</v>
@@ -12136,8 +13368,14 @@
       <c r="U165">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V165" t="s">
+        <v>29</v>
+      </c>
+      <c r="W165" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>48</v>
       </c>
@@ -12151,10 +13389,10 @@
         <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="F166" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="G166">
         <v>560.21799999999996</v>
@@ -12201,8 +13439,14 @@
       <c r="U166">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V166" t="s">
+        <v>29</v>
+      </c>
+      <c r="W166" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>48</v>
       </c>
@@ -12216,10 +13460,10 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>241</v>
+        <v>309</v>
       </c>
       <c r="F167" t="s">
-        <v>242</v>
+        <v>310</v>
       </c>
       <c r="G167">
         <v>280.65100000000001</v>
@@ -12266,8 +13510,14 @@
       <c r="U167">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V167" t="s">
+        <v>56</v>
+      </c>
+      <c r="W167" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>4</v>
       </c>
@@ -12281,10 +13531,10 @@
         <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>243</v>
+        <v>311</v>
       </c>
       <c r="F168" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="G168">
         <v>1901.673</v>
@@ -12331,8 +13581,14 @@
       <c r="U168">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V168" t="s">
+        <v>313</v>
+      </c>
+      <c r="W168" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>4</v>
       </c>
@@ -12346,10 +13602,10 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>244</v>
+        <v>312</v>
       </c>
       <c r="F169" t="s">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="G169">
         <v>261.56900000000002</v>
@@ -12396,8 +13652,14 @@
       <c r="U169">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V169" t="s">
+        <v>62</v>
+      </c>
+      <c r="W169" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>4</v>
       </c>
@@ -12411,10 +13673,10 @@
         <v>6</v>
       </c>
       <c r="E170" t="s">
-        <v>245</v>
+        <v>315</v>
       </c>
       <c r="F170" t="s">
-        <v>246</v>
+        <v>316</v>
       </c>
       <c r="G170">
         <v>1938.173</v>
@@ -12461,8 +13723,14 @@
       <c r="U170">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V170" t="s">
+        <v>317</v>
+      </c>
+      <c r="W170" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>50</v>
       </c>
@@ -12476,10 +13744,10 @@
         <v>8</v>
       </c>
       <c r="E171" t="s">
-        <v>247</v>
+        <v>319</v>
       </c>
       <c r="F171" t="s">
-        <v>248</v>
+        <v>320</v>
       </c>
       <c r="G171">
         <v>1323.45</v>
@@ -12526,8 +13794,14 @@
       <c r="U171">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V171" t="s">
+        <v>321</v>
+      </c>
+      <c r="W171" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>50</v>
       </c>
@@ -12541,10 +13815,10 @@
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>248</v>
+        <v>320</v>
       </c>
       <c r="F172" t="s">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="G172">
         <v>256.75599999999997</v>
@@ -12591,8 +13865,14 @@
       <c r="U172">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V172" t="s">
+        <v>29</v>
+      </c>
+      <c r="W172" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>50</v>
       </c>
@@ -12606,10 +13886,10 @@
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>249</v>
+        <v>323</v>
       </c>
       <c r="F173" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="G173">
         <v>53.308999999999997</v>
@@ -12656,8 +13936,14 @@
       <c r="U173">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V173" t="s">
+        <v>36</v>
+      </c>
+      <c r="W173" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>50</v>
       </c>
@@ -12671,10 +13957,10 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="F174" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="G174">
         <v>271.24400000000003</v>
@@ -12721,8 +14007,14 @@
       <c r="U174">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V174" t="s">
+        <v>29</v>
+      </c>
+      <c r="W174" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>51</v>
       </c>
@@ -12736,10 +14028,10 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>252</v>
+        <v>326</v>
       </c>
       <c r="F175" t="s">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="G175">
         <v>694.22799999999995</v>
@@ -12786,8 +14078,14 @@
       <c r="U175">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V175" t="s">
+        <v>33</v>
+      </c>
+      <c r="W175" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>51</v>
       </c>
@@ -12801,10 +14099,10 @@
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>253</v>
+        <v>327</v>
       </c>
       <c r="F176" t="s">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="G176">
         <v>524.29200000000003</v>
@@ -12851,8 +14149,14 @@
       <c r="U176">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V176" t="s">
+        <v>29</v>
+      </c>
+      <c r="W176" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>51</v>
       </c>
@@ -12866,10 +14170,10 @@
         <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>254</v>
+        <v>328</v>
       </c>
       <c r="F177" t="s">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="G177">
         <v>153.41</v>
@@ -12916,8 +14220,14 @@
       <c r="U177">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V177" t="s">
+        <v>29</v>
+      </c>
+      <c r="W177" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>51</v>
       </c>
@@ -12931,10 +14241,10 @@
         <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>256</v>
+        <v>330</v>
       </c>
       <c r="F178" t="s">
-        <v>257</v>
+        <v>331</v>
       </c>
       <c r="G178">
         <v>495.214</v>
@@ -12981,8 +14291,14 @@
       <c r="U178">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V178" t="s">
+        <v>42</v>
+      </c>
+      <c r="W178" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>51</v>
       </c>
@@ -12996,10 +14312,10 @@
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>257</v>
+        <v>331</v>
       </c>
       <c r="F179" t="s">
-        <v>258</v>
+        <v>332</v>
       </c>
       <c r="G179">
         <v>253.32900000000001</v>
@@ -13046,8 +14362,14 @@
       <c r="U179">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V179" t="s">
+        <v>29</v>
+      </c>
+      <c r="W179" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>51</v>
       </c>
@@ -13061,10 +14383,10 @@
         <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>258</v>
+        <v>332</v>
       </c>
       <c r="F180" t="s">
-        <v>259</v>
+        <v>333</v>
       </c>
       <c r="G180">
         <v>291.51499999999999</v>
@@ -13111,8 +14433,14 @@
       <c r="U180">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V180" t="s">
+        <v>334</v>
+      </c>
+      <c r="W180" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>52</v>
       </c>
@@ -13126,10 +14454,10 @@
         <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>260</v>
+        <v>336</v>
       </c>
       <c r="F181" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="G181">
         <v>1945.4490000000001</v>
@@ -13176,8 +14504,14 @@
       <c r="U181">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V181" t="s">
+        <v>131</v>
+      </c>
+      <c r="W181" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>53</v>
       </c>
@@ -13191,10 +14525,10 @@
         <v>5</v>
       </c>
       <c r="E182" t="s">
-        <v>262</v>
+        <v>338</v>
       </c>
       <c r="F182" t="s">
-        <v>263</v>
+        <v>339</v>
       </c>
       <c r="G182">
         <v>1791.9269999999999</v>
@@ -13241,8 +14575,14 @@
       <c r="U182">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V182" t="s">
+        <v>217</v>
+      </c>
+      <c r="W182" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>53</v>
       </c>
@@ -13256,10 +14596,10 @@
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>263</v>
+        <v>339</v>
       </c>
       <c r="F183" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="G183">
         <v>575.88199999999995</v>
@@ -13306,8 +14646,14 @@
       <c r="U183">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V183" t="s">
+        <v>29</v>
+      </c>
+      <c r="W183" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>53</v>
       </c>
@@ -13321,10 +14667,10 @@
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="F184" t="s">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="G184">
         <v>390.33800000000002</v>
@@ -13371,8 +14717,14 @@
       <c r="U184">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V184" t="s">
+        <v>29</v>
+      </c>
+      <c r="W184" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>5</v>
       </c>
@@ -13386,10 +14738,10 @@
         <v>5</v>
       </c>
       <c r="E185" t="s">
-        <v>266</v>
+        <v>342</v>
       </c>
       <c r="F185" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="G185">
         <v>1334.761</v>
@@ -13436,8 +14788,14 @@
       <c r="U185">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V185" t="s">
+        <v>102</v>
+      </c>
+      <c r="W185" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>5</v>
       </c>
@@ -13451,10 +14809,10 @@
         <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>267</v>
+        <v>343</v>
       </c>
       <c r="F186" t="s">
-        <v>268</v>
+        <v>344</v>
       </c>
       <c r="G186">
         <v>3522.2469999999998</v>
@@ -13501,8 +14859,14 @@
       <c r="U186">
         <v>2</v>
       </c>
-    </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V186" t="s">
+        <v>45</v>
+      </c>
+      <c r="W186" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>65</v>
       </c>
@@ -13516,10 +14880,10 @@
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>269</v>
+        <v>345</v>
       </c>
       <c r="F187" t="s">
-        <v>270</v>
+        <v>346</v>
       </c>
       <c r="G187">
         <v>136.62299999999999</v>
@@ -13566,8 +14930,14 @@
       <c r="U187">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V187" t="s">
+        <v>29</v>
+      </c>
+      <c r="W187" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>6</v>
       </c>
@@ -13581,10 +14951,10 @@
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>271</v>
+        <v>347</v>
       </c>
       <c r="F188" t="s">
-        <v>272</v>
+        <v>348</v>
       </c>
       <c r="G188">
         <v>1212.942</v>
@@ -13631,8 +15001,14 @@
       <c r="U188">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V188" t="s">
+        <v>56</v>
+      </c>
+      <c r="W188" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>6</v>
       </c>
@@ -13646,10 +15022,10 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>273</v>
+        <v>349</v>
       </c>
       <c r="F189" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="G189">
         <v>439.37299999999999</v>
@@ -13696,8 +15072,14 @@
       <c r="U189">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V189" t="s">
+        <v>162</v>
+      </c>
+      <c r="W189" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>6</v>
       </c>
@@ -13711,10 +15093,10 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="F190" t="s">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="G190">
         <v>145.673</v>
@@ -13761,8 +15143,14 @@
       <c r="U190">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V190" t="s">
+        <v>29</v>
+      </c>
+      <c r="W190" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>6</v>
       </c>
@@ -13776,10 +15164,10 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>276</v>
+        <v>352</v>
       </c>
       <c r="F191" t="s">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="G191">
         <v>264.03100000000001</v>
@@ -13826,8 +15214,14 @@
       <c r="U191">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V191" t="s">
+        <v>62</v>
+      </c>
+      <c r="W191" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>6</v>
       </c>
@@ -13841,10 +15235,10 @@
         <v>2</v>
       </c>
       <c r="E192" t="s">
-        <v>277</v>
+        <v>353</v>
       </c>
       <c r="F192" t="s">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="G192">
         <v>293.161</v>
@@ -13891,8 +15285,14 @@
       <c r="U192">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V192" t="s">
+        <v>29</v>
+      </c>
+      <c r="W192" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>6</v>
       </c>
@@ -13906,10 +15306,10 @@
         <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="F193" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="G193">
         <v>166.51599999999999</v>
@@ -13956,8 +15356,14 @@
       <c r="U193">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V193" t="s">
+        <v>29</v>
+      </c>
+      <c r="W193" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>6</v>
       </c>
@@ -13971,10 +15377,10 @@
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="F194" t="s">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="G194">
         <v>178.62299999999999</v>
@@ -14021,8 +15427,14 @@
       <c r="U194">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V194" t="s">
+        <v>29</v>
+      </c>
+      <c r="W194" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>6</v>
       </c>
@@ -14036,10 +15448,10 @@
         <v>3</v>
       </c>
       <c r="E195" t="s">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="F195" t="s">
-        <v>281</v>
+        <v>357</v>
       </c>
       <c r="G195">
         <v>300.98700000000002</v>
@@ -14086,8 +15498,14 @@
       <c r="U195">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V195" t="s">
+        <v>29</v>
+      </c>
+      <c r="W195" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>7</v>
       </c>
@@ -14101,10 +15519,10 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
       <c r="F196" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="G196">
         <v>363.834</v>
@@ -14151,8 +15569,14 @@
       <c r="U196">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V196" t="s">
+        <v>36</v>
+      </c>
+      <c r="W196" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>7</v>
       </c>
@@ -14166,10 +15590,10 @@
         <v>2</v>
       </c>
       <c r="E197" t="s">
-        <v>283</v>
+        <v>359</v>
       </c>
       <c r="F197" t="s">
-        <v>284</v>
+        <v>360</v>
       </c>
       <c r="G197">
         <v>306.89299999999997</v>
@@ -14216,8 +15640,14 @@
       <c r="U197">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V197" t="s">
+        <v>36</v>
+      </c>
+      <c r="W197" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>7</v>
       </c>
@@ -14231,10 +15661,10 @@
         <v>1</v>
       </c>
       <c r="E198" t="s">
-        <v>284</v>
+        <v>360</v>
       </c>
       <c r="F198" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
       <c r="G198">
         <v>43.689</v>
@@ -14281,8 +15711,14 @@
       <c r="U198">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V198" t="s">
+        <v>36</v>
+      </c>
+      <c r="W198" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>7</v>
       </c>
@@ -14296,10 +15732,10 @@
         <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>285</v>
+        <v>361</v>
       </c>
       <c r="F199" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="G199">
         <v>204.87799999999999</v>
@@ -14346,8 +15782,14 @@
       <c r="U199">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V199" t="s">
+        <v>188</v>
+      </c>
+      <c r="W199" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>7</v>
       </c>
@@ -14361,10 +15803,10 @@
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>287</v>
+        <v>363</v>
       </c>
       <c r="F200" t="s">
-        <v>288</v>
+        <v>364</v>
       </c>
       <c r="G200">
         <v>33.176000000000002</v>
@@ -14411,8 +15853,14 @@
       <c r="U200">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V200" t="s">
+        <v>36</v>
+      </c>
+      <c r="W200" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>7</v>
       </c>
@@ -14426,10 +15874,10 @@
         <v>7</v>
       </c>
       <c r="E201" t="s">
-        <v>289</v>
+        <v>365</v>
       </c>
       <c r="F201" t="s">
-        <v>290</v>
+        <v>366</v>
       </c>
       <c r="G201">
         <v>1414.277</v>
@@ -14476,8 +15924,14 @@
       <c r="U201">
         <v>0</v>
       </c>
-    </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V201" t="s">
+        <v>367</v>
+      </c>
+      <c r="W201" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>7</v>
       </c>
@@ -14491,10 +15945,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>290</v>
+        <v>366</v>
       </c>
       <c r="F202" t="s">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="G202">
         <v>236.52099999999999</v>
@@ -14541,8 +15995,14 @@
       <c r="U202">
         <v>0</v>
       </c>
-    </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V202" t="s">
+        <v>36</v>
+      </c>
+      <c r="W202" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>7</v>
       </c>
@@ -14556,10 +16016,10 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>291</v>
+        <v>369</v>
       </c>
       <c r="F203" t="s">
-        <v>292</v>
+        <v>370</v>
       </c>
       <c r="G203">
         <v>3.0000000000000001E-3</v>
@@ -14606,8 +16066,14 @@
       <c r="U203">
         <v>0</v>
       </c>
-    </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V203" t="s">
+        <v>36</v>
+      </c>
+      <c r="W203" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>8</v>
       </c>
@@ -14621,10 +16087,10 @@
         <v>3</v>
       </c>
       <c r="E204" t="s">
-        <v>293</v>
+        <v>371</v>
       </c>
       <c r="F204" t="s">
-        <v>294</v>
+        <v>372</v>
       </c>
       <c r="G204">
         <v>521.17200000000003</v>
@@ -14671,8 +16137,14 @@
       <c r="U204">
         <v>0</v>
       </c>
-    </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V204" t="s">
+        <v>36</v>
+      </c>
+      <c r="W204" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>8</v>
       </c>
@@ -14686,10 +16158,10 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>294</v>
+        <v>372</v>
       </c>
       <c r="F205" t="s">
-        <v>295</v>
+        <v>373</v>
       </c>
       <c r="G205">
         <v>458.50900000000001</v>
@@ -14736,8 +16208,14 @@
       <c r="U205">
         <v>0</v>
       </c>
-    </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V205" t="s">
+        <v>36</v>
+      </c>
+      <c r="W205" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>8</v>
       </c>
@@ -14751,10 +16229,10 @@
         <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>296</v>
+        <v>374</v>
       </c>
       <c r="F206" t="s">
-        <v>297</v>
+        <v>375</v>
       </c>
       <c r="G206">
         <v>1146.846</v>
@@ -14801,8 +16279,14 @@
       <c r="U206">
         <v>0</v>
       </c>
-    </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V206" t="s">
+        <v>178</v>
+      </c>
+      <c r="W206" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>8</v>
       </c>
@@ -14816,10 +16300,10 @@
         <v>13</v>
       </c>
       <c r="E207" t="s">
-        <v>298</v>
+        <v>376</v>
       </c>
       <c r="F207" t="s">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="G207">
         <v>2677.895</v>
@@ -14866,8 +16350,14 @@
       <c r="U207">
         <v>2</v>
       </c>
-    </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V207" t="s">
+        <v>378</v>
+      </c>
+      <c r="W207" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>9</v>
       </c>
@@ -14881,10 +16371,10 @@
         <v>7</v>
       </c>
       <c r="E208" t="s">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="F208" t="s">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="G208">
         <v>1421.896</v>
@@ -14931,8 +16421,14 @@
       <c r="U208">
         <v>0</v>
       </c>
-    </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V208" t="s">
+        <v>382</v>
+      </c>
+      <c r="W208" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="209" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>9</v>
       </c>
@@ -14946,10 +16442,10 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>301</v>
+        <v>381</v>
       </c>
       <c r="F209" t="s">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="G209">
         <v>379.99400000000003</v>
@@ -14996,8 +16492,14 @@
       <c r="U209">
         <v>0</v>
       </c>
-    </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V209" t="s">
+        <v>29</v>
+      </c>
+      <c r="W209" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="210" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>9</v>
       </c>
@@ -15011,10 +16513,10 @@
         <v>4</v>
       </c>
       <c r="E210" t="s">
-        <v>302</v>
+        <v>384</v>
       </c>
       <c r="F210" t="s">
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="G210">
         <v>284.67899999999997</v>
@@ -15061,8 +16563,14 @@
       <c r="U210">
         <v>0</v>
       </c>
-    </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V210" t="s">
+        <v>188</v>
+      </c>
+      <c r="W210" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="211" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>9</v>
       </c>
@@ -15076,10 +16584,10 @@
         <v>5</v>
       </c>
       <c r="E211" t="s">
-        <v>304</v>
+        <v>386</v>
       </c>
       <c r="F211" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="G211">
         <v>679.69</v>
@@ -15126,8 +16634,14 @@
       <c r="U211">
         <v>0</v>
       </c>
-    </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V211" t="s">
+        <v>388</v>
+      </c>
+      <c r="W211" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="212" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>9</v>
       </c>
@@ -15141,10 +16655,10 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="F212" t="s">
-        <v>306</v>
+        <v>390</v>
       </c>
       <c r="G212">
         <v>235.70599999999999</v>
@@ -15191,8 +16705,14 @@
       <c r="U212">
         <v>0</v>
       </c>
-    </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="V212" t="s">
+        <v>29</v>
+      </c>
+      <c r="W212" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>9</v>
       </c>
@@ -15206,10 +16726,10 @@
         <v>4</v>
       </c>
       <c r="E213" t="s">
-        <v>306</v>
+        <v>390</v>
       </c>
       <c r="F213" t="s">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="G213">
         <v>825.14700000000005</v>
@@ -15255,6 +16775,12 @@
       </c>
       <c r="U213">
         <v>0</v>
+      </c>
+      <c r="V213" t="s">
+        <v>392</v>
+      </c>
+      <c r="W213" t="s">
+        <v>393</v>
       </c>
     </row>
   </sheetData>

--- a/datosNiveles.xlsx
+++ b/datosNiveles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\hlocal\C_TFG\Datos\Mision Colombia-20260209T150018Z-3-001\jsonToCsv_TFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E6C76C-C4FE-4BD2-9836-D5B7630201D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6846BA-23F1-4202-B141-C3BECE25F00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="311">
   <si>
     <t>ID</t>
   </si>
@@ -97,36 +97,18 @@
     <t>15:20:46.000</t>
   </si>
   <si>
-    <t>78.57142857142857</t>
-  </si>
-  <si>
-    <t>21.42857142857143</t>
-  </si>
-  <si>
     <t>14:15:08.014</t>
   </si>
   <si>
     <t>14:18:26.124</t>
   </si>
   <si>
-    <t>100.0</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
     <t>14:33:17.624</t>
   </si>
   <si>
     <t>14:41:08.214</t>
   </si>
   <si>
-    <t>77.77777777777777</t>
-  </si>
-  <si>
-    <t>22.22222222222223</t>
-  </si>
-  <si>
     <t>14:41:36.785</t>
   </si>
   <si>
@@ -139,30 +121,12 @@
     <t>14:33:47.295</t>
   </si>
   <si>
-    <t>80.0</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
     <t>14:41:54.930</t>
   </si>
   <si>
-    <t>90.0</t>
-  </si>
-  <si>
-    <t>10.0</t>
-  </si>
-  <si>
     <t>14:45:59.368</t>
   </si>
   <si>
-    <t>83.33333333333333</t>
-  </si>
-  <si>
-    <t>16.66666666666667</t>
-  </si>
-  <si>
     <t>14:13:54.844</t>
   </si>
   <si>
@@ -190,12 +154,6 @@
     <t>14:33:28.259</t>
   </si>
   <si>
-    <t>75.0</t>
-  </si>
-  <si>
-    <t>25.0</t>
-  </si>
-  <si>
     <t>14:15:31.568</t>
   </si>
   <si>
@@ -208,12 +166,6 @@
     <t>14:40:03.212</t>
   </si>
   <si>
-    <t>85.71428571428571</t>
-  </si>
-  <si>
-    <t>14.285714285714292</t>
-  </si>
-  <si>
     <t>15:03:20.042</t>
   </si>
   <si>
@@ -229,9 +181,6 @@
     <t>15:40:07.396</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
     <t>15:42:48.934</t>
   </si>
   <si>
@@ -268,12 +217,6 @@
     <t>14:40:03.021</t>
   </si>
   <si>
-    <t>94.44444444444444</t>
-  </si>
-  <si>
-    <t>5.555555555555557</t>
-  </si>
-  <si>
     <t>14:45:28.196</t>
   </si>
   <si>
@@ -286,12 +229,6 @@
     <t>14:31:57.052</t>
   </si>
   <si>
-    <t>88.88888888888889</t>
-  </si>
-  <si>
-    <t>11.111111111111114</t>
-  </si>
-  <si>
     <t>14:37:24.618</t>
   </si>
   <si>
@@ -307,12 +244,6 @@
     <t>14:55:21.747</t>
   </si>
   <si>
-    <t>76.47058823529412</t>
-  </si>
-  <si>
-    <t>23.529411764705884</t>
-  </si>
-  <si>
     <t>14:56:41.369</t>
   </si>
   <si>
@@ -325,24 +256,12 @@
     <t>15:12:14.966</t>
   </si>
   <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>40.0</t>
-  </si>
-  <si>
     <t>15:06:50.654</t>
   </si>
   <si>
     <t>15:12:14.783</t>
   </si>
   <si>
-    <t>87.5</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
     <t>15:19:02.477</t>
   </si>
   <si>
@@ -358,12 +277,6 @@
     <t>14:43:21.606</t>
   </si>
   <si>
-    <t>76.92307692307692</t>
-  </si>
-  <si>
-    <t>23.07692307692308</t>
-  </si>
-  <si>
     <t>14:48:20.692</t>
   </si>
   <si>
@@ -400,12 +313,6 @@
     <t>15:51:25.871</t>
   </si>
   <si>
-    <t>90.47619047619048</t>
-  </si>
-  <si>
-    <t>9.523809523809518</t>
-  </si>
-  <si>
     <t>15:05:45.125</t>
   </si>
   <si>
@@ -415,21 +322,9 @@
     <t>15:21:30.015</t>
   </si>
   <si>
-    <t>86.66666666666667</t>
-  </si>
-  <si>
-    <t>13.333333333333329</t>
-  </si>
-  <si>
     <t>15:51:06.616</t>
   </si>
   <si>
-    <t>88.46153846153847</t>
-  </si>
-  <si>
-    <t>11.538461538461533</t>
-  </si>
-  <si>
     <t>15:51:06.619</t>
   </si>
   <si>
@@ -451,21 +346,9 @@
     <t>15:07:16.598</t>
   </si>
   <si>
-    <t>72.72727272727273</t>
-  </si>
-  <si>
-    <t>27.272727272727266</t>
-  </si>
-  <si>
     <t>15:53:03.221</t>
   </si>
   <si>
-    <t>93.93939393939394</t>
-  </si>
-  <si>
-    <t>6.060606060606062</t>
-  </si>
-  <si>
     <t>14:22:05.338</t>
   </si>
   <si>
@@ -490,12 +373,6 @@
     <t>15:19:31.478</t>
   </si>
   <si>
-    <t>73.6842105263158</t>
-  </si>
-  <si>
-    <t>26.315789473684205</t>
-  </si>
-  <si>
     <t>15:35:05.464</t>
   </si>
   <si>
@@ -508,12 +385,6 @@
     <t>15:13:30.278</t>
   </si>
   <si>
-    <t>90.9090909090909</t>
-  </si>
-  <si>
-    <t>9.090909090909093</t>
-  </si>
-  <si>
     <t>15:21:05.316</t>
   </si>
   <si>
@@ -532,12 +403,6 @@
     <t>15:42:14.394</t>
   </si>
   <si>
-    <t>79.16666666666667</t>
-  </si>
-  <si>
-    <t>20.83333333333333</t>
-  </si>
-  <si>
     <t>14:57:14.600</t>
   </si>
   <si>
@@ -556,12 +421,6 @@
     <t>15:37:20.923</t>
   </si>
   <si>
-    <t>71.42857142857143</t>
-  </si>
-  <si>
-    <t>28.57142857142857</t>
-  </si>
-  <si>
     <t>15:40:59.178</t>
   </si>
   <si>
@@ -586,36 +445,18 @@
     <t>15:42:01.441</t>
   </si>
   <si>
-    <t>66.66666666666667</t>
-  </si>
-  <si>
-    <t>33.33333333333333</t>
-  </si>
-  <si>
     <t>15:44:04.289</t>
   </si>
   <si>
     <t>15:53:09.504</t>
   </si>
   <si>
-    <t>54.54545454545455</t>
-  </si>
-  <si>
-    <t>45.45454545454545</t>
-  </si>
-  <si>
     <t>14:19:54.532</t>
   </si>
   <si>
     <t>14:50:35.180</t>
   </si>
   <si>
-    <t>86.36363636363636</t>
-  </si>
-  <si>
-    <t>13.63636363636364</t>
-  </si>
-  <si>
     <t>14:55:04.984</t>
   </si>
   <si>
@@ -643,12 +484,6 @@
     <t>15:35:37.780</t>
   </si>
   <si>
-    <t>72.5</t>
-  </si>
-  <si>
-    <t>27.5</t>
-  </si>
-  <si>
     <t>15:37:20.925</t>
   </si>
   <si>
@@ -673,24 +508,12 @@
     <t>15:53:16.524</t>
   </si>
   <si>
-    <t>81.25</t>
-  </si>
-  <si>
-    <t>18.75</t>
-  </si>
-  <si>
     <t>14:21:40.892</t>
   </si>
   <si>
     <t>14:44:31.489</t>
   </si>
   <si>
-    <t>92.3076923076923</t>
-  </si>
-  <si>
-    <t>7.692307692307693</t>
-  </si>
-  <si>
     <t>14:53:52.881</t>
   </si>
   <si>
@@ -883,12 +706,6 @@
     <t>15:32:58.880</t>
   </si>
   <si>
-    <t>93.33333333333333</t>
-  </si>
-  <si>
-    <t>6.666666666666671</t>
-  </si>
-  <si>
     <t>15:43:28.720</t>
   </si>
   <si>
@@ -916,21 +733,9 @@
     <t>15:05:24.859</t>
   </si>
   <si>
-    <t>35.714285714285715</t>
-  </si>
-  <si>
-    <t>64.28571428571428</t>
-  </si>
-  <si>
     <t>15:36:54.356</t>
   </si>
   <si>
-    <t>61.111111111111114</t>
-  </si>
-  <si>
-    <t>38.888888888888886</t>
-  </si>
-  <si>
     <t>16:00:54.514</t>
   </si>
   <si>
@@ -961,36 +766,18 @@
     <t>14:45:57.823</t>
   </si>
   <si>
-    <t>69.56521739130434</t>
-  </si>
-  <si>
-    <t>30.434782608695656</t>
-  </si>
-  <si>
     <t>14:50:19.392</t>
   </si>
   <si>
     <t>15:22:37.565</t>
   </si>
   <si>
-    <t>93.54838709677419</t>
-  </si>
-  <si>
-    <t>6.451612903225808</t>
-  </si>
-  <si>
     <t>16:50:34.650</t>
   </si>
   <si>
     <t>17:12:38.100</t>
   </si>
   <si>
-    <t>51.61290322580645</t>
-  </si>
-  <si>
-    <t>48.38709677419355</t>
-  </si>
-  <si>
     <t>17:16:54.856</t>
   </si>
   <si>
@@ -1024,12 +811,6 @@
     <t>14:32:00.853</t>
   </si>
   <si>
-    <t>88.23529411764706</t>
-  </si>
-  <si>
-    <t>11.764705882352942</t>
-  </si>
-  <si>
     <t>14:21:08.325</t>
   </si>
   <si>
@@ -1123,12 +904,6 @@
     <t>14:38:49.040</t>
   </si>
   <si>
-    <t>75.86206896551724</t>
-  </si>
-  <si>
-    <t>24.13793103448276</t>
-  </si>
-  <si>
     <t>14:42:45.561</t>
   </si>
   <si>
@@ -1156,24 +931,12 @@
     <t>14:58:20.061</t>
   </si>
   <si>
-    <t>76.0</t>
-  </si>
-  <si>
-    <t>24.0</t>
-  </si>
-  <si>
     <t>15:19:07.753</t>
   </si>
   <si>
     <t>15:42:49.649</t>
   </si>
   <si>
-    <t>93.75</t>
-  </si>
-  <si>
-    <t>6.25</t>
-  </si>
-  <si>
     <t>15:49:09.643</t>
   </si>
   <si>
@@ -1186,22 +949,10 @@
     <t>16:12:56.886</t>
   </si>
   <si>
-    <t>64.28571428571429</t>
-  </si>
-  <si>
-    <t>35.71428571428571</t>
-  </si>
-  <si>
     <t>16:16:52.592</t>
   </si>
   <si>
     <t>16:30:37.739</t>
-  </si>
-  <si>
-    <t>82.3529411764706</t>
-  </si>
-  <si>
-    <t>17.647058823529406</t>
   </si>
 </sst>
 </file>
@@ -1266,6 +1017,20 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1293,20 +1058,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1321,7 +1072,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D13D78F-AC41-4729-B506-72214316E2AA}" name="Tabla1" displayName="Tabla1" ref="A1:W213" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1D13D78F-AC41-4729-B506-72214316E2AA}" name="Tabla1" displayName="Tabla1" ref="A1:W213" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
   <autoFilter ref="A1:W213" xr:uid="{1D13D78F-AC41-4729-B506-72214316E2AA}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{26CFCA52-95FF-4CE8-9413-A359BC904B01}" name="ID"/>
@@ -1795,11 +1546,11 @@
       <c r="U2">
         <v>0</v>
       </c>
-      <c r="V2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" t="s">
-        <v>26</v>
+      <c r="V2">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W2">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -1816,10 +1567,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>198.11</v>
@@ -1866,11 +1617,11 @@
       <c r="U3">
         <v>0</v>
       </c>
-      <c r="V3" t="s">
-        <v>29</v>
-      </c>
-      <c r="W3" t="s">
-        <v>30</v>
+      <c r="V3">
+        <v>100</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -1887,10 +1638,10 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G4">
         <v>891.5</v>
@@ -1937,11 +1688,11 @@
       <c r="U4">
         <v>1</v>
       </c>
-      <c r="V4" t="s">
-        <v>29</v>
-      </c>
-      <c r="W4" t="s">
-        <v>30</v>
+      <c r="V4">
+        <v>100</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -1958,10 +1709,10 @@
         <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G5">
         <v>470.59</v>
@@ -2008,11 +1759,11 @@
       <c r="U5">
         <v>1</v>
       </c>
-      <c r="V5" t="s">
-        <v>33</v>
-      </c>
-      <c r="W5" t="s">
-        <v>34</v>
+      <c r="V5">
+        <v>77.7777777777777</v>
+      </c>
+      <c r="W5">
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -2029,10 +1780,10 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G6">
         <v>28.571000000000002</v>
@@ -2080,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="V6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -2100,10 +1851,10 @@
         <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G7">
         <v>698.94299999999998</v>
@@ -2150,11 +1901,11 @@
       <c r="U7">
         <v>0</v>
       </c>
-      <c r="V7" t="s">
-        <v>39</v>
-      </c>
-      <c r="W7" t="s">
-        <v>40</v>
+      <c r="V7">
+        <v>80</v>
+      </c>
+      <c r="W7">
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -2171,10 +1922,10 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G8">
         <v>487.63499999999999</v>
@@ -2221,11 +1972,11 @@
       <c r="U8">
         <v>1</v>
       </c>
-      <c r="V8" t="s">
-        <v>42</v>
-      </c>
-      <c r="W8" t="s">
-        <v>43</v>
+      <c r="V8">
+        <v>90</v>
+      </c>
+      <c r="W8">
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -2242,10 +1993,10 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>244.43799999999999</v>
@@ -2292,11 +2043,11 @@
       <c r="U9">
         <v>0</v>
       </c>
-      <c r="V9" t="s">
-        <v>45</v>
-      </c>
-      <c r="W9" t="s">
-        <v>46</v>
+      <c r="V9">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W9">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -2313,10 +2064,10 @@
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G10">
         <v>377.255</v>
@@ -2363,11 +2114,11 @@
       <c r="U10">
         <v>0</v>
       </c>
-      <c r="V10" t="s">
-        <v>33</v>
-      </c>
-      <c r="W10" t="s">
-        <v>34</v>
+      <c r="V10">
+        <v>77.7777777777777</v>
+      </c>
+      <c r="W10">
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -2384,10 +2135,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G11">
         <v>221.697</v>
@@ -2434,11 +2185,11 @@
       <c r="U11">
         <v>0</v>
       </c>
-      <c r="V11" t="s">
-        <v>29</v>
-      </c>
-      <c r="W11" t="s">
-        <v>30</v>
+      <c r="V11">
+        <v>100</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -2455,10 +2206,10 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G12">
         <v>324.53300000000002</v>
@@ -2505,11 +2256,11 @@
       <c r="U12">
         <v>0</v>
       </c>
-      <c r="V12" t="s">
-        <v>45</v>
-      </c>
-      <c r="W12" t="s">
-        <v>46</v>
+      <c r="V12">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W12">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -2526,10 +2277,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G13">
         <v>3.0000000000000001E-3</v>
@@ -2577,10 +2328,10 @@
         <v>0</v>
       </c>
       <c r="V13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W13" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -2597,10 +2348,10 @@
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G14">
         <v>395.01100000000002</v>
@@ -2647,11 +2398,11 @@
       <c r="U14">
         <v>0</v>
       </c>
-      <c r="V14" t="s">
-        <v>29</v>
-      </c>
-      <c r="W14" t="s">
-        <v>30</v>
+      <c r="V14">
+        <v>100</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2668,10 +2419,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G15">
         <v>251.125</v>
@@ -2718,11 +2469,11 @@
       <c r="U15">
         <v>0</v>
       </c>
-      <c r="V15" t="s">
-        <v>29</v>
-      </c>
-      <c r="W15" t="s">
-        <v>30</v>
+      <c r="V15">
+        <v>100</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2739,10 +2490,10 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G16">
         <v>165.10400000000001</v>
@@ -2789,11 +2540,11 @@
       <c r="U16">
         <v>1</v>
       </c>
-      <c r="V16" t="s">
-        <v>56</v>
-      </c>
-      <c r="W16" t="s">
-        <v>57</v>
+      <c r="V16">
+        <v>75</v>
+      </c>
+      <c r="W16">
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2810,10 +2561,10 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G17">
         <v>766.95100000000002</v>
@@ -2860,11 +2611,11 @@
       <c r="U17">
         <v>0</v>
       </c>
-      <c r="V17" t="s">
-        <v>29</v>
-      </c>
-      <c r="W17" t="s">
-        <v>30</v>
+      <c r="V17">
+        <v>100</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2881,10 +2632,10 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G18">
         <v>412.25</v>
@@ -2931,11 +2682,11 @@
       <c r="U18">
         <v>1</v>
       </c>
-      <c r="V18" t="s">
-        <v>29</v>
-      </c>
-      <c r="W18" t="s">
-        <v>30</v>
+      <c r="V18">
+        <v>100</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2952,10 +2703,10 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G19">
         <v>292.44299999999998</v>
@@ -3002,11 +2753,11 @@
       <c r="U19">
         <v>0</v>
       </c>
-      <c r="V19" t="s">
-        <v>62</v>
-      </c>
-      <c r="W19" t="s">
-        <v>63</v>
+      <c r="V19">
+        <v>85.714285714285694</v>
+      </c>
+      <c r="W19">
+        <v>14.285714285714199</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -3023,10 +2774,10 @@
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="G20">
         <v>675.44</v>
@@ -3074,10 +2825,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -3094,10 +2845,10 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G21">
         <v>331.98099999999999</v>
@@ -3145,10 +2896,10 @@
         <v>2</v>
       </c>
       <c r="V21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -3165,10 +2916,10 @@
         <v>4</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G22">
         <v>625.00599999999997</v>
@@ -3215,11 +2966,11 @@
       <c r="U22">
         <v>0</v>
       </c>
-      <c r="V22" t="s">
-        <v>69</v>
-      </c>
-      <c r="W22" t="s">
-        <v>69</v>
+      <c r="V22">
+        <v>50</v>
+      </c>
+      <c r="W22">
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -3236,10 +2987,10 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="G23">
         <v>161.53800000000001</v>
@@ -3286,11 +3037,11 @@
       <c r="U23">
         <v>1</v>
       </c>
-      <c r="V23" t="s">
-        <v>30</v>
-      </c>
-      <c r="W23" t="s">
-        <v>29</v>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -3307,10 +3058,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="F24" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G24">
         <v>191.298</v>
@@ -3357,11 +3108,11 @@
       <c r="U24">
         <v>0</v>
       </c>
-      <c r="V24" t="s">
-        <v>29</v>
-      </c>
-      <c r="W24" t="s">
-        <v>30</v>
+      <c r="V24">
+        <v>100</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3378,10 +3129,10 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F25" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="G25">
         <v>590.29700000000003</v>
@@ -3428,11 +3179,11 @@
       <c r="U25">
         <v>1</v>
       </c>
-      <c r="V25" t="s">
-        <v>56</v>
-      </c>
-      <c r="W25" t="s">
-        <v>57</v>
+      <c r="V25">
+        <v>75</v>
+      </c>
+      <c r="W25">
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -3449,10 +3200,10 @@
         <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F26" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="G26">
         <v>425.238</v>
@@ -3499,11 +3250,11 @@
       <c r="U26">
         <v>1</v>
       </c>
-      <c r="V26" t="s">
-        <v>29</v>
-      </c>
-      <c r="W26" t="s">
-        <v>30</v>
+      <c r="V26">
+        <v>100</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -3520,10 +3271,10 @@
         <v>2</v>
       </c>
       <c r="E27" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="G27">
         <v>514.99199999999996</v>
@@ -3570,11 +3321,11 @@
       <c r="U27">
         <v>0</v>
       </c>
-      <c r="V27" t="s">
-        <v>29</v>
-      </c>
-      <c r="W27" t="s">
-        <v>30</v>
+      <c r="V27">
+        <v>100</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3591,10 +3342,10 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="G28">
         <v>226.94800000000001</v>
@@ -3641,11 +3392,11 @@
       <c r="U28">
         <v>0</v>
       </c>
-      <c r="V28" t="s">
-        <v>29</v>
-      </c>
-      <c r="W28" t="s">
-        <v>30</v>
+      <c r="V28">
+        <v>100</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -3662,10 +3413,10 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="G29">
         <v>239.91</v>
@@ -3712,11 +3463,11 @@
       <c r="U29">
         <v>1</v>
       </c>
-      <c r="V29" t="s">
-        <v>29</v>
-      </c>
-      <c r="W29" t="s">
-        <v>30</v>
+      <c r="V29">
+        <v>100</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -3733,10 +3484,10 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="G30">
         <v>350.96199999999999</v>
@@ -3783,11 +3534,11 @@
       <c r="U30">
         <v>2</v>
       </c>
-      <c r="V30" t="s">
-        <v>29</v>
-      </c>
-      <c r="W30" t="s">
-        <v>30</v>
+      <c r="V30">
+        <v>100</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3804,10 +3555,10 @@
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G31">
         <v>445.16</v>
@@ -3854,11 +3605,11 @@
       <c r="U31">
         <v>0</v>
       </c>
-      <c r="V31" t="s">
-        <v>56</v>
-      </c>
-      <c r="W31" t="s">
-        <v>57</v>
+      <c r="V31">
+        <v>75</v>
+      </c>
+      <c r="W31">
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3875,10 +3626,10 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F32" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="G32">
         <v>1019.31</v>
@@ -3925,11 +3676,11 @@
       <c r="U32">
         <v>0</v>
       </c>
-      <c r="V32" t="s">
-        <v>82</v>
-      </c>
-      <c r="W32" t="s">
-        <v>83</v>
+      <c r="V32">
+        <v>94.4444444444444</v>
+      </c>
+      <c r="W32">
+        <v>5.55555555555555</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3946,10 +3697,10 @@
         <v>2</v>
       </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="F33" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="G33">
         <v>325.17500000000001</v>
@@ -3996,11 +3747,11 @@
       <c r="U33">
         <v>0</v>
       </c>
-      <c r="V33" t="s">
-        <v>39</v>
-      </c>
-      <c r="W33" t="s">
-        <v>40</v>
+      <c r="V33">
+        <v>80</v>
+      </c>
+      <c r="W33">
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -4017,10 +3768,10 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G34">
         <v>114.916</v>
@@ -4067,11 +3818,11 @@
       <c r="U34">
         <v>0</v>
       </c>
-      <c r="V34" t="s">
-        <v>29</v>
-      </c>
-      <c r="W34" t="s">
-        <v>30</v>
+      <c r="V34">
+        <v>100</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -4088,10 +3839,10 @@
         <v>4</v>
       </c>
       <c r="E35" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G35">
         <v>1033.24</v>
@@ -4138,11 +3889,11 @@
       <c r="U35">
         <v>0</v>
       </c>
-      <c r="V35" t="s">
-        <v>88</v>
-      </c>
-      <c r="W35" t="s">
-        <v>89</v>
+      <c r="V35">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W35">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -4159,10 +3910,10 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="F36" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="G36">
         <v>327.56599999999997</v>
@@ -4209,11 +3960,11 @@
       <c r="U36">
         <v>0</v>
       </c>
-      <c r="V36" t="s">
-        <v>29</v>
-      </c>
-      <c r="W36" t="s">
-        <v>30</v>
+      <c r="V36">
+        <v>100</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -4230,10 +3981,10 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F37" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="G37">
         <v>391.79300000000001</v>
@@ -4280,11 +4031,11 @@
       <c r="U37">
         <v>0</v>
       </c>
-      <c r="V37" t="s">
-        <v>29</v>
-      </c>
-      <c r="W37" t="s">
-        <v>30</v>
+      <c r="V37">
+        <v>100</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -4301,10 +4052,10 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="G38">
         <v>53.040999999999997</v>
@@ -4352,10 +4103,10 @@
         <v>1</v>
       </c>
       <c r="V38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -4372,10 +4123,10 @@
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F39" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="G39">
         <v>830.96100000000001</v>
@@ -4422,11 +4173,11 @@
       <c r="U39">
         <v>0</v>
       </c>
-      <c r="V39" t="s">
-        <v>95</v>
-      </c>
-      <c r="W39" t="s">
-        <v>96</v>
+      <c r="V39">
+        <v>76.470588235294102</v>
+      </c>
+      <c r="W39">
+        <v>23.529411764705799</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -4443,10 +4194,10 @@
         <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="G40">
         <v>203.50800000000001</v>
@@ -4493,11 +4244,11 @@
       <c r="U40">
         <v>0</v>
       </c>
-      <c r="V40" t="s">
-        <v>29</v>
-      </c>
-      <c r="W40" t="s">
-        <v>30</v>
+      <c r="V40">
+        <v>100</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -4514,10 +4265,10 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F41" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="G41">
         <v>240.90199999999999</v>
@@ -4564,11 +4315,11 @@
       <c r="U41">
         <v>0</v>
       </c>
-      <c r="V41" t="s">
-        <v>29</v>
-      </c>
-      <c r="W41" t="s">
-        <v>30</v>
+      <c r="V41">
+        <v>100</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -4585,10 +4336,10 @@
         <v>4</v>
       </c>
       <c r="E42" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="F42" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="G42">
         <v>489.18700000000001</v>
@@ -4635,11 +4386,11 @@
       <c r="U42">
         <v>0</v>
       </c>
-      <c r="V42" t="s">
-        <v>101</v>
-      </c>
-      <c r="W42" t="s">
-        <v>102</v>
+      <c r="V42">
+        <v>60</v>
+      </c>
+      <c r="W42">
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -4656,10 +4407,10 @@
         <v>2</v>
       </c>
       <c r="E43" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="F43" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="G43">
         <v>324.12900000000002</v>
@@ -4706,11 +4457,11 @@
       <c r="U43">
         <v>0</v>
       </c>
-      <c r="V43" t="s">
-        <v>105</v>
-      </c>
-      <c r="W43" t="s">
-        <v>106</v>
+      <c r="V43">
+        <v>87.5</v>
+      </c>
+      <c r="W43">
+        <v>12.5</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
@@ -4727,10 +4478,10 @@
         <v>2</v>
       </c>
       <c r="E44" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="F44" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="G44">
         <v>407.69400000000002</v>
@@ -4777,11 +4528,11 @@
       <c r="U44">
         <v>1</v>
       </c>
-      <c r="V44" t="s">
-        <v>45</v>
-      </c>
-      <c r="W44" t="s">
-        <v>46</v>
+      <c r="V44">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W44">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
@@ -4798,10 +4549,10 @@
         <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="F45" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="G45">
         <v>1489.634</v>
@@ -4848,11 +4599,11 @@
       <c r="U45">
         <v>0</v>
       </c>
-      <c r="V45" t="s">
-        <v>39</v>
-      </c>
-      <c r="W45" t="s">
-        <v>40</v>
+      <c r="V45">
+        <v>80</v>
+      </c>
+      <c r="W45">
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
@@ -4869,10 +4620,10 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F46" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="G46">
         <v>3.0000000000000001E-3</v>
@@ -4920,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W46" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
@@ -4940,10 +4691,10 @@
         <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="F47" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="G47">
         <v>1244.95</v>
@@ -4990,11 +4741,11 @@
       <c r="U47">
         <v>0</v>
       </c>
-      <c r="V47" t="s">
-        <v>112</v>
-      </c>
-      <c r="W47" t="s">
-        <v>113</v>
+      <c r="V47">
+        <v>76.923076923076906</v>
+      </c>
+      <c r="W47">
+        <v>23.076923076922998</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
@@ -5011,10 +4762,10 @@
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="F48" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="G48">
         <v>299.08600000000001</v>
@@ -5061,11 +4812,11 @@
       <c r="U48">
         <v>0</v>
       </c>
-      <c r="V48" t="s">
-        <v>29</v>
-      </c>
-      <c r="W48" t="s">
-        <v>30</v>
+      <c r="V48">
+        <v>100</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
@@ -5082,10 +4833,10 @@
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="F49" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="G49">
         <v>150.49600000000001</v>
@@ -5132,11 +4883,11 @@
       <c r="U49">
         <v>0</v>
       </c>
-      <c r="V49" t="s">
-        <v>29</v>
-      </c>
-      <c r="W49" t="s">
-        <v>30</v>
+      <c r="V49">
+        <v>100</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.3">
@@ -5153,10 +4904,10 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="F50" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="G50">
         <v>337.06</v>
@@ -5203,11 +4954,11 @@
       <c r="U50">
         <v>0</v>
       </c>
-      <c r="V50" t="s">
-        <v>29</v>
-      </c>
-      <c r="W50" t="s">
-        <v>30</v>
+      <c r="V50">
+        <v>100</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.3">
@@ -5224,10 +4975,10 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="F51" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="G51">
         <v>344.19799999999998</v>
@@ -5274,11 +5025,11 @@
       <c r="U51">
         <v>0</v>
       </c>
-      <c r="V51" t="s">
-        <v>29</v>
-      </c>
-      <c r="W51" t="s">
-        <v>30</v>
+      <c r="V51">
+        <v>100</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.3">
@@ -5295,10 +5046,10 @@
         <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="F52" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="G52">
         <v>379.60599999999999</v>
@@ -5345,11 +5096,11 @@
       <c r="U52">
         <v>0</v>
       </c>
-      <c r="V52" t="s">
-        <v>62</v>
-      </c>
-      <c r="W52" t="s">
-        <v>63</v>
+      <c r="V52">
+        <v>85.714285714285694</v>
+      </c>
+      <c r="W52">
+        <v>14.285714285714199</v>
       </c>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.3">
@@ -5366,10 +5117,10 @@
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="F53" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="G53">
         <v>430.90499999999997</v>
@@ -5417,10 +5168,10 @@
         <v>0</v>
       </c>
       <c r="V53" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W53" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.3">
@@ -5437,10 +5188,10 @@
         <v>5</v>
       </c>
       <c r="E54" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="F54" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="G54">
         <v>784.26300000000003</v>
@@ -5487,11 +5238,11 @@
       <c r="U54">
         <v>0</v>
       </c>
-      <c r="V54" t="s">
-        <v>29</v>
-      </c>
-      <c r="W54" t="s">
-        <v>30</v>
+      <c r="V54">
+        <v>100</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.3">
@@ -5508,10 +5259,10 @@
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="F55" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="G55">
         <v>239.89599999999999</v>
@@ -5558,11 +5309,11 @@
       <c r="U55">
         <v>0</v>
       </c>
-      <c r="V55" t="s">
-        <v>56</v>
-      </c>
-      <c r="W55" t="s">
-        <v>57</v>
+      <c r="V55">
+        <v>75</v>
+      </c>
+      <c r="W55">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.3">
@@ -5579,10 +5330,10 @@
         <v>4</v>
       </c>
       <c r="E56" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="F56" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="G56">
         <v>546.42399999999998</v>
@@ -5629,11 +5380,11 @@
       <c r="U56">
         <v>0</v>
       </c>
-      <c r="V56" t="s">
-        <v>126</v>
-      </c>
-      <c r="W56" t="s">
-        <v>127</v>
+      <c r="V56">
+        <v>90.476190476190396</v>
+      </c>
+      <c r="W56">
+        <v>9.5238095238095095</v>
       </c>
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.3">
@@ -5650,10 +5401,10 @@
         <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="F57" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="G57">
         <v>459.43299999999999</v>
@@ -5700,11 +5451,11 @@
       <c r="U57">
         <v>0</v>
       </c>
-      <c r="V57" t="s">
-        <v>29</v>
-      </c>
-      <c r="W57" t="s">
-        <v>30</v>
+      <c r="V57">
+        <v>100</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.3">
@@ -5721,10 +5472,10 @@
         <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="F58" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="G58">
         <v>485.45699999999999</v>
@@ -5771,11 +5522,11 @@
       <c r="U58">
         <v>1</v>
       </c>
-      <c r="V58" t="s">
-        <v>131</v>
-      </c>
-      <c r="W58" t="s">
-        <v>132</v>
+      <c r="V58">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W58">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.3">
@@ -5792,10 +5543,10 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="F59" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="G59">
         <v>1776.6010000000001</v>
@@ -5842,11 +5593,11 @@
       <c r="U59">
         <v>0</v>
       </c>
-      <c r="V59" t="s">
-        <v>134</v>
-      </c>
-      <c r="W59" t="s">
-        <v>135</v>
+      <c r="V59">
+        <v>88.461538461538396</v>
+      </c>
+      <c r="W59">
+        <v>11.538461538461499</v>
       </c>
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.3">
@@ -5863,10 +5614,10 @@
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="F60" t="s">
-        <v>136</v>
+        <v>101</v>
       </c>
       <c r="G60">
         <v>3.0000000000000001E-3</v>
@@ -5914,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="V60" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W60" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.3">
@@ -5934,10 +5685,10 @@
         <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>137</v>
+        <v>102</v>
       </c>
       <c r="F61" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="G61">
         <v>321.52800000000002</v>
@@ -5985,10 +5736,10 @@
         <v>0</v>
       </c>
       <c r="V61" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W61" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.3">
@@ -6005,10 +5756,10 @@
         <v>4</v>
       </c>
       <c r="E62" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="F62" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="G62">
         <v>1034.588</v>
@@ -6055,11 +5806,11 @@
       <c r="U62">
         <v>0</v>
       </c>
-      <c r="V62" t="s">
-        <v>29</v>
-      </c>
-      <c r="W62" t="s">
-        <v>30</v>
+      <c r="V62">
+        <v>100</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.3">
@@ -6076,10 +5827,10 @@
         <v>2</v>
       </c>
       <c r="E63" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F63" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="G63">
         <v>283.024</v>
@@ -6126,11 +5877,11 @@
       <c r="U63">
         <v>0</v>
       </c>
-      <c r="V63" t="s">
-        <v>88</v>
-      </c>
-      <c r="W63" t="s">
-        <v>89</v>
+      <c r="V63">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W63">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.3">
@@ -6147,10 +5898,10 @@
         <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="F64" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="G64">
         <v>465.21699999999998</v>
@@ -6197,11 +5948,11 @@
       <c r="U64">
         <v>0</v>
       </c>
-      <c r="V64" t="s">
-        <v>143</v>
-      </c>
-      <c r="W64" t="s">
-        <v>144</v>
+      <c r="V64">
+        <v>72.727272727272705</v>
+      </c>
+      <c r="W64">
+        <v>27.272727272727199</v>
       </c>
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.3">
@@ -6218,10 +5969,10 @@
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="F65" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="G65">
         <v>2746.623</v>
@@ -6268,11 +6019,11 @@
       <c r="U65">
         <v>0</v>
       </c>
-      <c r="V65" t="s">
-        <v>146</v>
-      </c>
-      <c r="W65" t="s">
-        <v>147</v>
+      <c r="V65">
+        <v>93.939393939393895</v>
+      </c>
+      <c r="W65">
+        <v>6.0606060606060597</v>
       </c>
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.3">
@@ -6289,10 +6040,10 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="F66" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="G66">
         <v>1745.9690000000001</v>
@@ -6339,11 +6090,11 @@
       <c r="U66">
         <v>0</v>
       </c>
-      <c r="V66" t="s">
-        <v>25</v>
-      </c>
-      <c r="W66" t="s">
-        <v>26</v>
+      <c r="V66">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W66">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.3">
@@ -6360,10 +6111,10 @@
         <v>2</v>
       </c>
       <c r="E67" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="F67" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="G67">
         <v>136.61600000000001</v>
@@ -6411,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="V67" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W67" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.3">
@@ -6431,10 +6182,10 @@
         <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="F68" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="G68">
         <v>539.26599999999996</v>
@@ -6482,10 +6233,10 @@
         <v>1</v>
       </c>
       <c r="V68" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W68" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.3">
@@ -6502,10 +6253,10 @@
         <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>152</v>
+        <v>113</v>
       </c>
       <c r="F69" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="G69">
         <v>596.93200000000002</v>
@@ -6552,11 +6303,11 @@
       <c r="U69">
         <v>3</v>
       </c>
-      <c r="V69" t="s">
-        <v>69</v>
-      </c>
-      <c r="W69" t="s">
-        <v>69</v>
+      <c r="V69">
+        <v>50</v>
+      </c>
+      <c r="W69">
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.3">
@@ -6573,10 +6324,10 @@
         <v>5</v>
       </c>
       <c r="E70" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="F70" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="G70">
         <v>1086.9169999999999</v>
@@ -6623,11 +6374,11 @@
       <c r="U70">
         <v>0</v>
       </c>
-      <c r="V70" t="s">
-        <v>156</v>
-      </c>
-      <c r="W70" t="s">
-        <v>157</v>
+      <c r="V70">
+        <v>73.684210526315795</v>
+      </c>
+      <c r="W70">
+        <v>26.315789473684202</v>
       </c>
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.3">
@@ -6644,10 +6395,10 @@
         <v>4</v>
       </c>
       <c r="E71" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="F71" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="G71">
         <v>933.98599999999999</v>
@@ -6694,11 +6445,11 @@
       <c r="U71">
         <v>0</v>
       </c>
-      <c r="V71" t="s">
-        <v>56</v>
-      </c>
-      <c r="W71" t="s">
-        <v>57</v>
+      <c r="V71">
+        <v>75</v>
+      </c>
+      <c r="W71">
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.3">
@@ -6715,10 +6466,10 @@
         <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="F72" t="s">
-        <v>159</v>
+        <v>118</v>
       </c>
       <c r="G72">
         <v>955.89599999999996</v>
@@ -6765,11 +6516,11 @@
       <c r="U72">
         <v>0</v>
       </c>
-      <c r="V72" t="s">
-        <v>45</v>
-      </c>
-      <c r="W72" t="s">
-        <v>46</v>
+      <c r="V72">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W72">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.3">
@@ -6786,10 +6537,10 @@
         <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="F73" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="G73">
         <v>1026.5830000000001</v>
@@ -6836,11 +6587,11 @@
       <c r="U73">
         <v>0</v>
       </c>
-      <c r="V73" t="s">
-        <v>162</v>
-      </c>
-      <c r="W73" t="s">
-        <v>163</v>
+      <c r="V73">
+        <v>90.909090909090907</v>
+      </c>
+      <c r="W73">
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.3">
@@ -6857,10 +6608,10 @@
         <v>2</v>
       </c>
       <c r="E74" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="F74" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="G74">
         <v>455.03800000000001</v>
@@ -6907,11 +6658,11 @@
       <c r="U74">
         <v>1</v>
       </c>
-      <c r="V74" t="s">
-        <v>29</v>
-      </c>
-      <c r="W74" t="s">
-        <v>30</v>
+      <c r="V74">
+        <v>100</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.3">
@@ -6928,10 +6679,10 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="F75" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="G75">
         <v>113.578</v>
@@ -6978,11 +6729,11 @@
       <c r="U75">
         <v>0</v>
       </c>
-      <c r="V75" t="s">
-        <v>29</v>
-      </c>
-      <c r="W75" t="s">
-        <v>30</v>
+      <c r="V75">
+        <v>100</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.3">
@@ -6999,10 +6750,10 @@
         <v>2</v>
       </c>
       <c r="E76" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="F76" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="G76">
         <v>340.90100000000001</v>
@@ -7049,11 +6800,11 @@
       <c r="U76">
         <v>0</v>
       </c>
-      <c r="V76" t="s">
-        <v>29</v>
-      </c>
-      <c r="W76" t="s">
-        <v>30</v>
+      <c r="V76">
+        <v>100</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.3">
@@ -7070,10 +6821,10 @@
         <v>6</v>
       </c>
       <c r="E77" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="F77" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="G77">
         <v>1365.6410000000001</v>
@@ -7120,11 +6871,11 @@
       <c r="U77">
         <v>0</v>
       </c>
-      <c r="V77" t="s">
-        <v>82</v>
-      </c>
-      <c r="W77" t="s">
-        <v>83</v>
+      <c r="V77">
+        <v>94.4444444444444</v>
+      </c>
+      <c r="W77">
+        <v>5.55555555555555</v>
       </c>
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.3">
@@ -7141,10 +6892,10 @@
         <v>7</v>
       </c>
       <c r="E78" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="F78" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="G78">
         <v>982.15499999999997</v>
@@ -7191,11 +6942,11 @@
       <c r="U78">
         <v>0</v>
       </c>
-      <c r="V78" t="s">
-        <v>170</v>
-      </c>
-      <c r="W78" t="s">
-        <v>171</v>
+      <c r="V78">
+        <v>79.1666666666666</v>
+      </c>
+      <c r="W78">
+        <v>20.8333333333333</v>
       </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.3">
@@ -7212,10 +6963,10 @@
         <v>6</v>
       </c>
       <c r="E79" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="F79" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="G79">
         <v>1539.473</v>
@@ -7262,11 +7013,11 @@
       <c r="U79">
         <v>1</v>
       </c>
-      <c r="V79" t="s">
-        <v>29</v>
-      </c>
-      <c r="W79" t="s">
-        <v>30</v>
+      <c r="V79">
+        <v>100</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.3">
@@ -7283,10 +7034,10 @@
         <v>1</v>
       </c>
       <c r="E80" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="F80" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="G80">
         <v>182.26300000000001</v>
@@ -7334,10 +7085,10 @@
         <v>1</v>
       </c>
       <c r="V80" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W80" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.3">
@@ -7354,10 +7105,10 @@
         <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="F81" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="G81">
         <v>577.74199999999996</v>
@@ -7404,11 +7155,11 @@
       <c r="U81">
         <v>0</v>
       </c>
-      <c r="V81" t="s">
-        <v>62</v>
-      </c>
-      <c r="W81" t="s">
-        <v>63</v>
+      <c r="V81">
+        <v>85.714285714285694</v>
+      </c>
+      <c r="W81">
+        <v>14.285714285714199</v>
       </c>
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.3">
@@ -7425,10 +7176,10 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="F82" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="G82">
         <v>1772.241</v>
@@ -7475,11 +7226,11 @@
       <c r="U82">
         <v>2</v>
       </c>
-      <c r="V82" t="s">
-        <v>178</v>
-      </c>
-      <c r="W82" t="s">
-        <v>179</v>
+      <c r="V82">
+        <v>71.428571428571402</v>
+      </c>
+      <c r="W82">
+        <v>28.571428571428498</v>
       </c>
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.3">
@@ -7496,10 +7247,10 @@
         <v>2</v>
       </c>
       <c r="E83" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="F83" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="G83">
         <v>218.255</v>
@@ -7547,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="V83" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W83" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.3">
@@ -7567,10 +7318,10 @@
         <v>5</v>
       </c>
       <c r="E84" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="F84" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="G84">
         <v>847.82100000000003</v>
@@ -7617,11 +7368,11 @@
       <c r="U84">
         <v>0</v>
       </c>
-      <c r="V84" t="s">
-        <v>101</v>
-      </c>
-      <c r="W84" t="s">
-        <v>102</v>
+      <c r="V84">
+        <v>60</v>
+      </c>
+      <c r="W84">
+        <v>40</v>
       </c>
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.3">
@@ -7638,10 +7389,10 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="F85" t="s">
-        <v>183</v>
+        <v>136</v>
       </c>
       <c r="G85">
         <v>76.603999999999999</v>
@@ -7689,10 +7440,10 @@
         <v>0</v>
       </c>
       <c r="V85" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W85" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.3">
@@ -7709,10 +7460,10 @@
         <v>2</v>
       </c>
       <c r="E86" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="F86" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="G86">
         <v>293.68299999999999</v>
@@ -7759,11 +7510,11 @@
       <c r="U86">
         <v>0</v>
       </c>
-      <c r="V86" t="s">
-        <v>29</v>
-      </c>
-      <c r="W86" t="s">
-        <v>30</v>
+      <c r="V86">
+        <v>100</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.3">
@@ -7780,10 +7531,10 @@
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="F87" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="G87">
         <v>1589.087</v>
@@ -7830,11 +7581,11 @@
       <c r="U87">
         <v>2</v>
       </c>
-      <c r="V87" t="s">
-        <v>29</v>
-      </c>
-      <c r="W87" t="s">
-        <v>30</v>
+      <c r="V87">
+        <v>100</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.3">
@@ -7851,10 +7602,10 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>186</v>
+        <v>139</v>
       </c>
       <c r="F88" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="G88">
         <v>188.63200000000001</v>
@@ -7901,11 +7652,11 @@
       <c r="U88">
         <v>0</v>
       </c>
-      <c r="V88" t="s">
-        <v>188</v>
-      </c>
-      <c r="W88" t="s">
-        <v>189</v>
+      <c r="V88">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W88">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.3">
@@ -7922,10 +7673,10 @@
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="F89" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="G89">
         <v>122.848</v>
@@ -7973,10 +7724,10 @@
         <v>1</v>
       </c>
       <c r="V89" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W89" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.3">
@@ -7993,10 +7744,10 @@
         <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>190</v>
+        <v>141</v>
       </c>
       <c r="F90" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="G90">
         <v>545.21500000000003</v>
@@ -8043,11 +7794,11 @@
       <c r="U90">
         <v>0</v>
       </c>
-      <c r="V90" t="s">
-        <v>192</v>
-      </c>
-      <c r="W90" t="s">
-        <v>193</v>
+      <c r="V90">
+        <v>54.545454545454497</v>
+      </c>
+      <c r="W90">
+        <v>45.454545454545404</v>
       </c>
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.3">
@@ -8064,10 +7815,10 @@
         <v>9</v>
       </c>
       <c r="E91" t="s">
-        <v>194</v>
+        <v>143</v>
       </c>
       <c r="F91" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="G91">
         <v>1840.6479999999999</v>
@@ -8114,11 +7865,11 @@
       <c r="U91">
         <v>0</v>
       </c>
-      <c r="V91" t="s">
-        <v>196</v>
-      </c>
-      <c r="W91" t="s">
-        <v>197</v>
+      <c r="V91">
+        <v>86.363636363636303</v>
+      </c>
+      <c r="W91">
+        <v>13.636363636363599</v>
       </c>
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.3">
@@ -8135,10 +7886,10 @@
         <v>2</v>
       </c>
       <c r="E92" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="F92" t="s">
-        <v>198</v>
+        <v>145</v>
       </c>
       <c r="G92">
         <v>269.80399999999997</v>
@@ -8185,11 +7936,11 @@
       <c r="U92">
         <v>1</v>
       </c>
-      <c r="V92" t="s">
-        <v>29</v>
-      </c>
-      <c r="W92" t="s">
-        <v>30</v>
+      <c r="V92">
+        <v>100</v>
+      </c>
+      <c r="W92">
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.3">
@@ -8206,10 +7957,10 @@
         <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="F93" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="G93">
         <v>387.76600000000002</v>
@@ -8256,11 +8007,11 @@
       <c r="U93">
         <v>0</v>
       </c>
-      <c r="V93" t="s">
-        <v>29</v>
-      </c>
-      <c r="W93" t="s">
-        <v>30</v>
+      <c r="V93">
+        <v>100</v>
+      </c>
+      <c r="W93">
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.3">
@@ -8277,10 +8028,10 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="F94" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="G94">
         <v>269.32299999999998</v>
@@ -8327,11 +8078,11 @@
       <c r="U94">
         <v>0</v>
       </c>
-      <c r="V94" t="s">
-        <v>29</v>
-      </c>
-      <c r="W94" t="s">
-        <v>30</v>
+      <c r="V94">
+        <v>100</v>
+      </c>
+      <c r="W94">
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.3">
@@ -8348,10 +8099,10 @@
         <v>6</v>
       </c>
       <c r="E95" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="F95" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="G95">
         <v>1126.18</v>
@@ -8398,11 +8149,11 @@
       <c r="U95">
         <v>0</v>
       </c>
-      <c r="V95" t="s">
-        <v>178</v>
-      </c>
-      <c r="W95" t="s">
-        <v>179</v>
+      <c r="V95">
+        <v>71.428571428571402</v>
+      </c>
+      <c r="W95">
+        <v>28.571428571428498</v>
       </c>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.3">
@@ -8419,10 +8170,10 @@
         <v>2</v>
       </c>
       <c r="E96" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="F96" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="G96">
         <v>327.07600000000002</v>
@@ -8469,11 +8220,11 @@
       <c r="U96">
         <v>0</v>
       </c>
-      <c r="V96" t="s">
-        <v>39</v>
-      </c>
-      <c r="W96" t="s">
-        <v>40</v>
+      <c r="V96">
+        <v>80</v>
+      </c>
+      <c r="W96">
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.3">
@@ -8490,10 +8241,10 @@
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>204</v>
+        <v>151</v>
       </c>
       <c r="F97" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="G97">
         <v>243.67</v>
@@ -8540,11 +8291,11 @@
       <c r="U97">
         <v>0</v>
       </c>
-      <c r="V97" t="s">
-        <v>29</v>
-      </c>
-      <c r="W97" t="s">
-        <v>30</v>
+      <c r="V97">
+        <v>100</v>
+      </c>
+      <c r="W97">
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.3">
@@ -8561,10 +8312,10 @@
         <v>7</v>
       </c>
       <c r="E98" t="s">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="F98" t="s">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="G98">
         <v>1501.88</v>
@@ -8611,11 +8362,11 @@
       <c r="U98">
         <v>2</v>
       </c>
-      <c r="V98" t="s">
-        <v>207</v>
-      </c>
-      <c r="W98" t="s">
-        <v>208</v>
+      <c r="V98">
+        <v>72.5</v>
+      </c>
+      <c r="W98">
+        <v>27.5</v>
       </c>
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.3">
@@ -8632,10 +8383,10 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="F99" t="s">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="G99">
         <v>103.145</v>
@@ -8683,10 +8434,10 @@
         <v>0</v>
       </c>
       <c r="V99" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W99" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.3">
@@ -8703,10 +8454,10 @@
         <v>2</v>
       </c>
       <c r="E100" t="s">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="F100" t="s">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="G100">
         <v>307.60000000000002</v>
@@ -8753,11 +8504,11 @@
       <c r="U100">
         <v>0</v>
       </c>
-      <c r="V100" t="s">
-        <v>39</v>
-      </c>
-      <c r="W100" t="s">
-        <v>40</v>
+      <c r="V100">
+        <v>80</v>
+      </c>
+      <c r="W100">
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.3">
@@ -8774,10 +8525,10 @@
         <v>4</v>
       </c>
       <c r="E101" t="s">
-        <v>211</v>
+        <v>156</v>
       </c>
       <c r="F101" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="G101">
         <v>626.35299999999995</v>
@@ -8824,11 +8575,11 @@
       <c r="U101">
         <v>0</v>
       </c>
-      <c r="V101" t="s">
-        <v>29</v>
-      </c>
-      <c r="W101" t="s">
-        <v>30</v>
+      <c r="V101">
+        <v>100</v>
+      </c>
+      <c r="W101">
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.3">
@@ -8845,10 +8596,10 @@
         <v>7</v>
       </c>
       <c r="E102" t="s">
-        <v>212</v>
+        <v>157</v>
       </c>
       <c r="F102" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="G102">
         <v>1181.2190000000001</v>
@@ -8895,11 +8646,11 @@
       <c r="U102">
         <v>3</v>
       </c>
-      <c r="V102" t="s">
-        <v>88</v>
-      </c>
-      <c r="W102" t="s">
-        <v>89</v>
+      <c r="V102">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W102">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.3">
@@ -8916,10 +8667,10 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>214</v>
+        <v>159</v>
       </c>
       <c r="F103" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="G103">
         <v>349.72500000000002</v>
@@ -8966,11 +8717,11 @@
       <c r="U103">
         <v>0</v>
       </c>
-      <c r="V103" t="s">
-        <v>29</v>
-      </c>
-      <c r="W103" t="s">
-        <v>30</v>
+      <c r="V103">
+        <v>100</v>
+      </c>
+      <c r="W103">
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.3">
@@ -8987,10 +8738,10 @@
         <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>215</v>
+        <v>160</v>
       </c>
       <c r="F104" t="s">
-        <v>216</v>
+        <v>161</v>
       </c>
       <c r="G104">
         <v>2901.125</v>
@@ -9037,11 +8788,11 @@
       <c r="U104">
         <v>3</v>
       </c>
-      <c r="V104" t="s">
-        <v>217</v>
-      </c>
-      <c r="W104" t="s">
-        <v>218</v>
+      <c r="V104">
+        <v>81.25</v>
+      </c>
+      <c r="W104">
+        <v>18.75</v>
       </c>
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.3">
@@ -9058,10 +8809,10 @@
         <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>219</v>
+        <v>162</v>
       </c>
       <c r="F105" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="G105">
         <v>1370.597</v>
@@ -9108,11 +8859,11 @@
       <c r="U105">
         <v>0</v>
       </c>
-      <c r="V105" t="s">
-        <v>221</v>
-      </c>
-      <c r="W105" t="s">
-        <v>222</v>
+      <c r="V105">
+        <v>92.307692307692307</v>
+      </c>
+      <c r="W105">
+        <v>7.6923076923076898</v>
       </c>
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.3">
@@ -9129,10 +8880,10 @@
         <v>4</v>
       </c>
       <c r="E106" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="F106" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="G106">
         <v>561.39200000000005</v>
@@ -9179,11 +8930,11 @@
       <c r="U106">
         <v>1</v>
       </c>
-      <c r="V106" t="s">
-        <v>131</v>
-      </c>
-      <c r="W106" t="s">
-        <v>132</v>
+      <c r="V106">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W106">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.3">
@@ -9200,10 +8951,10 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>224</v>
+        <v>165</v>
       </c>
       <c r="F107" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="G107">
         <v>346.435</v>
@@ -9250,11 +9001,11 @@
       <c r="U107">
         <v>0</v>
       </c>
-      <c r="V107" t="s">
-        <v>29</v>
-      </c>
-      <c r="W107" t="s">
-        <v>30</v>
+      <c r="V107">
+        <v>100</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.3">
@@ -9271,10 +9022,10 @@
         <v>2</v>
       </c>
       <c r="E108" t="s">
-        <v>225</v>
+        <v>166</v>
       </c>
       <c r="F108" t="s">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="G108">
         <v>318.33100000000002</v>
@@ -9321,11 +9072,11 @@
       <c r="U108">
         <v>0</v>
       </c>
-      <c r="V108" t="s">
-        <v>56</v>
-      </c>
-      <c r="W108" t="s">
-        <v>57</v>
+      <c r="V108">
+        <v>75</v>
+      </c>
+      <c r="W108">
+        <v>25</v>
       </c>
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.3">
@@ -9342,10 +9093,10 @@
         <v>1</v>
       </c>
       <c r="E109" t="s">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="F109" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="G109">
         <v>116.30200000000001</v>
@@ -9392,11 +9143,11 @@
       <c r="U109">
         <v>0</v>
       </c>
-      <c r="V109" t="s">
-        <v>29</v>
-      </c>
-      <c r="W109" t="s">
-        <v>30</v>
+      <c r="V109">
+        <v>100</v>
+      </c>
+      <c r="W109">
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.3">
@@ -9413,10 +9164,10 @@
         <v>6</v>
       </c>
       <c r="E110" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="F110" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="G110">
         <v>1462.615</v>
@@ -9464,10 +9215,10 @@
         <v>0</v>
       </c>
       <c r="V110" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W110" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.3">
@@ -9484,10 +9235,10 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="F111" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="G111">
         <v>254.846</v>
@@ -9535,10 +9286,10 @@
         <v>0</v>
       </c>
       <c r="V111" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W111" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.3">
@@ -9555,10 +9306,10 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>231</v>
+        <v>172</v>
       </c>
       <c r="F112" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="G112">
         <v>924.37099999999998</v>
@@ -9606,10 +9357,10 @@
         <v>0</v>
       </c>
       <c r="V112" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W112" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.3">
@@ -9626,10 +9377,10 @@
         <v>3</v>
       </c>
       <c r="E113" t="s">
-        <v>232</v>
+        <v>173</v>
       </c>
       <c r="F113" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="G113">
         <v>88.405000000000001</v>
@@ -9677,10 +9428,10 @@
         <v>0</v>
       </c>
       <c r="V113" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W113" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.3">
@@ -9697,10 +9448,10 @@
         <v>1</v>
       </c>
       <c r="E114" t="s">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="F114" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="G114">
         <v>245.28100000000001</v>
@@ -9748,10 +9499,10 @@
         <v>0</v>
       </c>
       <c r="V114" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W114" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.3">
@@ -9768,10 +9519,10 @@
         <v>1</v>
       </c>
       <c r="E115" t="s">
-        <v>235</v>
+        <v>176</v>
       </c>
       <c r="F115" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="G115">
         <v>234.22200000000001</v>
@@ -9819,10 +9570,10 @@
         <v>0</v>
       </c>
       <c r="V115" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W115" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.3">
@@ -9839,10 +9590,10 @@
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>236</v>
+        <v>177</v>
       </c>
       <c r="F116" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="G116">
         <v>217.36199999999999</v>
@@ -9890,10 +9641,10 @@
         <v>0</v>
       </c>
       <c r="V116" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W116" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.3">
@@ -9910,10 +9661,10 @@
         <v>6</v>
       </c>
       <c r="E117" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="F117" t="s">
-        <v>238</v>
+        <v>179</v>
       </c>
       <c r="G117">
         <v>1188.2809999999999</v>
@@ -9961,10 +9712,10 @@
         <v>4</v>
       </c>
       <c r="V117" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W117" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.3">
@@ -9981,10 +9732,10 @@
         <v>5</v>
       </c>
       <c r="E118" t="s">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="F118" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="G118">
         <v>974.44600000000003</v>
@@ -10031,11 +9782,11 @@
       <c r="U118">
         <v>0</v>
       </c>
-      <c r="V118" t="s">
-        <v>39</v>
-      </c>
-      <c r="W118" t="s">
-        <v>40</v>
+      <c r="V118">
+        <v>80</v>
+      </c>
+      <c r="W118">
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.3">
@@ -10052,10 +9803,10 @@
         <v>4</v>
       </c>
       <c r="E119" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="F119" t="s">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="G119">
         <v>934.26599999999996</v>
@@ -10102,11 +9853,11 @@
       <c r="U119">
         <v>1</v>
       </c>
-      <c r="V119" t="s">
-        <v>88</v>
-      </c>
-      <c r="W119" t="s">
-        <v>89</v>
+      <c r="V119">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W119">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.3">
@@ -10123,10 +9874,10 @@
         <v>3</v>
       </c>
       <c r="E120" t="s">
-        <v>241</v>
+        <v>182</v>
       </c>
       <c r="F120" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="G120">
         <v>519.375</v>
@@ -10173,11 +9924,11 @@
       <c r="U120">
         <v>0</v>
       </c>
-      <c r="V120" t="s">
-        <v>178</v>
-      </c>
-      <c r="W120" t="s">
-        <v>179</v>
+      <c r="V120">
+        <v>71.428571428571402</v>
+      </c>
+      <c r="W120">
+        <v>28.571428571428498</v>
       </c>
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.3">
@@ -10194,10 +9945,10 @@
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="F121" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="G121">
         <v>287.03899999999999</v>
@@ -10244,11 +9995,11 @@
       <c r="U121">
         <v>1</v>
       </c>
-      <c r="V121" t="s">
-        <v>56</v>
-      </c>
-      <c r="W121" t="s">
-        <v>57</v>
+      <c r="V121">
+        <v>75</v>
+      </c>
+      <c r="W121">
+        <v>25</v>
       </c>
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.3">
@@ -10265,10 +10016,10 @@
         <v>1</v>
       </c>
       <c r="E122" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="F122" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="G122">
         <v>254.63399999999999</v>
@@ -10315,11 +10066,11 @@
       <c r="U122">
         <v>0</v>
       </c>
-      <c r="V122" t="s">
-        <v>29</v>
-      </c>
-      <c r="W122" t="s">
-        <v>30</v>
+      <c r="V122">
+        <v>100</v>
+      </c>
+      <c r="W122">
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.3">
@@ -10336,10 +10087,10 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="F123" t="s">
-        <v>245</v>
+        <v>186</v>
       </c>
       <c r="G123">
         <v>151.352</v>
@@ -10386,11 +10137,11 @@
       <c r="U123">
         <v>0</v>
       </c>
-      <c r="V123" t="s">
-        <v>29</v>
-      </c>
-      <c r="W123" t="s">
-        <v>30</v>
+      <c r="V123">
+        <v>100</v>
+      </c>
+      <c r="W123">
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.3">
@@ -10407,10 +10158,10 @@
         <v>4</v>
       </c>
       <c r="E124" t="s">
-        <v>246</v>
+        <v>187</v>
       </c>
       <c r="F124" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="G124">
         <v>802.04100000000005</v>
@@ -10457,11 +10208,11 @@
       <c r="U124">
         <v>0</v>
       </c>
-      <c r="V124" t="s">
-        <v>29</v>
-      </c>
-      <c r="W124" t="s">
-        <v>30</v>
+      <c r="V124">
+        <v>100</v>
+      </c>
+      <c r="W124">
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.3">
@@ -10478,10 +10229,10 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>247</v>
+        <v>188</v>
       </c>
       <c r="F125" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="G125">
         <v>255.15600000000001</v>
@@ -10528,11 +10279,11 @@
       <c r="U125">
         <v>0</v>
       </c>
-      <c r="V125" t="s">
-        <v>188</v>
-      </c>
-      <c r="W125" t="s">
-        <v>189</v>
+      <c r="V125">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W125">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.3">
@@ -10549,10 +10300,10 @@
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>248</v>
+        <v>189</v>
       </c>
       <c r="F126" t="s">
-        <v>249</v>
+        <v>190</v>
       </c>
       <c r="G126">
         <v>157.999</v>
@@ -10599,11 +10350,11 @@
       <c r="U126">
         <v>0</v>
       </c>
-      <c r="V126" t="s">
-        <v>29</v>
-      </c>
-      <c r="W126" t="s">
-        <v>30</v>
+      <c r="V126">
+        <v>100</v>
+      </c>
+      <c r="W126">
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.3">
@@ -10620,10 +10371,10 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>249</v>
+        <v>190</v>
       </c>
       <c r="F127" t="s">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="G127">
         <v>410.64400000000001</v>
@@ -10670,11 +10421,11 @@
       <c r="U127">
         <v>1</v>
       </c>
-      <c r="V127" t="s">
-        <v>188</v>
-      </c>
-      <c r="W127" t="s">
-        <v>189</v>
+      <c r="V127">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W127">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.3">
@@ -10691,10 +10442,10 @@
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="F128" t="s">
-        <v>251</v>
+        <v>192</v>
       </c>
       <c r="G128">
         <v>195.59299999999999</v>
@@ -10741,11 +10492,11 @@
       <c r="U128">
         <v>0</v>
       </c>
-      <c r="V128" t="s">
-        <v>101</v>
-      </c>
-      <c r="W128" t="s">
-        <v>102</v>
+      <c r="V128">
+        <v>60</v>
+      </c>
+      <c r="W128">
+        <v>40</v>
       </c>
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.3">
@@ -10762,10 +10513,10 @@
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>251</v>
+        <v>192</v>
       </c>
       <c r="F129" t="s">
-        <v>252</v>
+        <v>193</v>
       </c>
       <c r="G129">
         <v>146.059</v>
@@ -10812,11 +10563,11 @@
       <c r="U129">
         <v>0</v>
       </c>
-      <c r="V129" t="s">
-        <v>29</v>
-      </c>
-      <c r="W129" t="s">
-        <v>30</v>
+      <c r="V129">
+        <v>100</v>
+      </c>
+      <c r="W129">
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.3">
@@ -10833,10 +10584,10 @@
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>253</v>
+        <v>194</v>
       </c>
       <c r="F130" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="G130">
         <v>416.86200000000002</v>
@@ -10883,11 +10634,11 @@
       <c r="U130">
         <v>0</v>
       </c>
-      <c r="V130" t="s">
-        <v>105</v>
-      </c>
-      <c r="W130" t="s">
-        <v>106</v>
+      <c r="V130">
+        <v>87.5</v>
+      </c>
+      <c r="W130">
+        <v>12.5</v>
       </c>
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.3">
@@ -10904,10 +10655,10 @@
         <v>1</v>
       </c>
       <c r="E131" t="s">
-        <v>254</v>
+        <v>195</v>
       </c>
       <c r="F131" t="s">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="G131">
         <v>281.108</v>
@@ -10954,11 +10705,11 @@
       <c r="U131">
         <v>2</v>
       </c>
-      <c r="V131" t="s">
-        <v>29</v>
-      </c>
-      <c r="W131" t="s">
-        <v>30</v>
+      <c r="V131">
+        <v>100</v>
+      </c>
+      <c r="W131">
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.3">
@@ -10975,10 +10726,10 @@
         <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="F132" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="G132">
         <v>222.53200000000001</v>
@@ -11025,11 +10776,11 @@
       <c r="U132">
         <v>0</v>
       </c>
-      <c r="V132" t="s">
-        <v>29</v>
-      </c>
-      <c r="W132" t="s">
-        <v>30</v>
+      <c r="V132">
+        <v>100</v>
+      </c>
+      <c r="W132">
+        <v>0</v>
       </c>
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.3">
@@ -11046,10 +10797,10 @@
         <v>1</v>
       </c>
       <c r="E133" t="s">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="F133" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
       <c r="G133">
         <v>207.91800000000001</v>
@@ -11096,11 +10847,11 @@
       <c r="U133">
         <v>0</v>
       </c>
-      <c r="V133" t="s">
-        <v>29</v>
-      </c>
-      <c r="W133" t="s">
-        <v>30</v>
+      <c r="V133">
+        <v>100</v>
+      </c>
+      <c r="W133">
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.3">
@@ -11117,10 +10868,10 @@
         <v>2</v>
       </c>
       <c r="E134" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
       <c r="F134" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="G134">
         <v>438.53899999999999</v>
@@ -11167,11 +10918,11 @@
       <c r="U134">
         <v>0</v>
       </c>
-      <c r="V134" t="s">
-        <v>29</v>
-      </c>
-      <c r="W134" t="s">
-        <v>30</v>
+      <c r="V134">
+        <v>100</v>
+      </c>
+      <c r="W134">
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.3">
@@ -11188,10 +10939,10 @@
         <v>1</v>
       </c>
       <c r="E135" t="s">
-        <v>259</v>
+        <v>200</v>
       </c>
       <c r="F135" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="G135">
         <v>7.0000000000000001E-3</v>
@@ -11239,10 +10990,10 @@
         <v>0</v>
       </c>
       <c r="V135" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W135" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.3">
@@ -11259,10 +11010,10 @@
         <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>261</v>
+        <v>202</v>
       </c>
       <c r="F136" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="G136">
         <v>379.57499999999999</v>
@@ -11310,10 +11061,10 @@
         <v>0</v>
       </c>
       <c r="V136" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W136" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.3">
@@ -11330,10 +11081,10 @@
         <v>2</v>
       </c>
       <c r="E137" t="s">
-        <v>263</v>
+        <v>204</v>
       </c>
       <c r="F137" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="G137">
         <v>361.988</v>
@@ -11380,11 +11131,11 @@
       <c r="U137">
         <v>0</v>
       </c>
-      <c r="V137" t="s">
-        <v>56</v>
-      </c>
-      <c r="W137" t="s">
-        <v>57</v>
+      <c r="V137">
+        <v>75</v>
+      </c>
+      <c r="W137">
+        <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.3">
@@ -11401,10 +11152,10 @@
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>264</v>
+        <v>205</v>
       </c>
       <c r="F138" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="G138">
         <v>293.10599999999999</v>
@@ -11451,11 +11202,11 @@
       <c r="U138">
         <v>1</v>
       </c>
-      <c r="V138" t="s">
-        <v>29</v>
-      </c>
-      <c r="W138" t="s">
-        <v>30</v>
+      <c r="V138">
+        <v>100</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.3">
@@ -11472,10 +11223,10 @@
         <v>4</v>
       </c>
       <c r="E139" t="s">
-        <v>265</v>
+        <v>206</v>
       </c>
       <c r="F139" t="s">
-        <v>266</v>
+        <v>207</v>
       </c>
       <c r="G139">
         <v>530.96</v>
@@ -11522,11 +11273,11 @@
       <c r="U139">
         <v>0</v>
       </c>
-      <c r="V139" t="s">
-        <v>25</v>
-      </c>
-      <c r="W139" t="s">
-        <v>26</v>
+      <c r="V139">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W139">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.3">
@@ -11543,10 +11294,10 @@
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>266</v>
+        <v>207</v>
       </c>
       <c r="F140" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="G140">
         <v>3.0000000000000001E-3</v>
@@ -11594,10 +11345,10 @@
         <v>0</v>
       </c>
       <c r="V140" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W140" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.3">
@@ -11614,10 +11365,10 @@
         <v>2</v>
       </c>
       <c r="E141" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="F141" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="G141">
         <v>326.041</v>
@@ -11665,10 +11416,10 @@
         <v>0</v>
       </c>
       <c r="V141" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W141" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.3">
@@ -11685,10 +11436,10 @@
         <v>3</v>
       </c>
       <c r="E142" t="s">
-        <v>269</v>
+        <v>210</v>
       </c>
       <c r="F142" t="s">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="G142">
         <v>802.67700000000002</v>
@@ -11736,10 +11487,10 @@
         <v>2</v>
       </c>
       <c r="V142" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W142" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.3">
@@ -11756,10 +11507,10 @@
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>270</v>
+        <v>211</v>
       </c>
       <c r="F143" t="s">
-        <v>271</v>
+        <v>212</v>
       </c>
       <c r="G143">
         <v>3.0000000000000001E-3</v>
@@ -11807,10 +11558,10 @@
         <v>0</v>
       </c>
       <c r="V143" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W143" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.3">
@@ -11827,10 +11578,10 @@
         <v>10</v>
       </c>
       <c r="E144" t="s">
-        <v>272</v>
+        <v>213</v>
       </c>
       <c r="F144" t="s">
-        <v>273</v>
+        <v>214</v>
       </c>
       <c r="G144">
         <v>1324.8530000000001</v>
@@ -11877,11 +11628,11 @@
       <c r="U144">
         <v>0</v>
       </c>
-      <c r="V144" t="s">
-        <v>88</v>
-      </c>
-      <c r="W144" t="s">
-        <v>89</v>
+      <c r="V144">
+        <v>88.8888888888888</v>
+      </c>
+      <c r="W144">
+        <v>11.1111111111111</v>
       </c>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.3">
@@ -11898,10 +11649,10 @@
         <v>4</v>
       </c>
       <c r="E145" t="s">
-        <v>274</v>
+        <v>215</v>
       </c>
       <c r="F145" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="G145">
         <v>718.51300000000003</v>
@@ -11948,11 +11699,11 @@
       <c r="U145">
         <v>0</v>
       </c>
-      <c r="V145" t="s">
-        <v>112</v>
-      </c>
-      <c r="W145" t="s">
-        <v>113</v>
+      <c r="V145">
+        <v>76.923076923076906</v>
+      </c>
+      <c r="W145">
+        <v>23.076923076922998</v>
       </c>
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.3">
@@ -11969,10 +11720,10 @@
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>275</v>
+        <v>216</v>
       </c>
       <c r="F146" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="G146">
         <v>250.69399999999999</v>
@@ -12019,11 +11770,11 @@
       <c r="U146">
         <v>2</v>
       </c>
-      <c r="V146" t="s">
-        <v>45</v>
-      </c>
-      <c r="W146" t="s">
-        <v>46</v>
+      <c r="V146">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W146">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.3">
@@ -12040,10 +11791,10 @@
         <v>2</v>
       </c>
       <c r="E147" t="s">
-        <v>276</v>
+        <v>217</v>
       </c>
       <c r="F147" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
       <c r="G147">
         <v>276.25599999999997</v>
@@ -12090,11 +11841,11 @@
       <c r="U147">
         <v>0</v>
       </c>
-      <c r="V147" t="s">
-        <v>25</v>
-      </c>
-      <c r="W147" t="s">
-        <v>26</v>
+      <c r="V147">
+        <v>78.571428571428498</v>
+      </c>
+      <c r="W147">
+        <v>21.428571428571399</v>
       </c>
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.3">
@@ -12111,10 +11862,10 @@
         <v>1</v>
       </c>
       <c r="E148" t="s">
-        <v>278</v>
+        <v>219</v>
       </c>
       <c r="F148" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="G148">
         <v>213.15899999999999</v>
@@ -12162,10 +11913,10 @@
         <v>0</v>
       </c>
       <c r="V148" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W148" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.3">
@@ -12182,10 +11933,10 @@
         <v>3</v>
       </c>
       <c r="E149" t="s">
-        <v>279</v>
+        <v>220</v>
       </c>
       <c r="F149" t="s">
-        <v>280</v>
+        <v>221</v>
       </c>
       <c r="G149">
         <v>531.59</v>
@@ -12233,10 +11984,10 @@
         <v>1</v>
       </c>
       <c r="V149" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W149" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.3">
@@ -12253,10 +12004,10 @@
         <v>4</v>
       </c>
       <c r="E150" t="s">
-        <v>281</v>
+        <v>222</v>
       </c>
       <c r="F150" t="s">
-        <v>282</v>
+        <v>223</v>
       </c>
       <c r="G150">
         <v>688.51300000000003</v>
@@ -12303,11 +12054,11 @@
       <c r="U150">
         <v>1</v>
       </c>
-      <c r="V150" t="s">
-        <v>29</v>
-      </c>
-      <c r="W150" t="s">
-        <v>30</v>
+      <c r="V150">
+        <v>100</v>
+      </c>
+      <c r="W150">
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.3">
@@ -12324,10 +12075,10 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>282</v>
+        <v>223</v>
       </c>
       <c r="F151" t="s">
-        <v>283</v>
+        <v>224</v>
       </c>
       <c r="G151">
         <v>436.10700000000003</v>
@@ -12374,11 +12125,11 @@
       <c r="U151">
         <v>4</v>
       </c>
-      <c r="V151" t="s">
-        <v>30</v>
-      </c>
-      <c r="W151" t="s">
-        <v>29</v>
+      <c r="V151">
+        <v>0</v>
+      </c>
+      <c r="W151">
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.3">
@@ -12395,10 +12146,10 @@
         <v>2</v>
       </c>
       <c r="E152" t="s">
-        <v>284</v>
+        <v>225</v>
       </c>
       <c r="F152" t="s">
-        <v>285</v>
+        <v>226</v>
       </c>
       <c r="G152">
         <v>666.76099999999997</v>
@@ -12445,11 +12196,11 @@
       <c r="U152">
         <v>0</v>
       </c>
-      <c r="V152" t="s">
-        <v>62</v>
-      </c>
-      <c r="W152" t="s">
-        <v>63</v>
+      <c r="V152">
+        <v>85.714285714285694</v>
+      </c>
+      <c r="W152">
+        <v>14.285714285714199</v>
       </c>
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.3">
@@ -12466,10 +12217,10 @@
         <v>4</v>
       </c>
       <c r="E153" t="s">
-        <v>285</v>
+        <v>226</v>
       </c>
       <c r="F153" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="G153">
         <v>1686.739</v>
@@ -12516,11 +12267,11 @@
       <c r="U153">
         <v>6</v>
       </c>
-      <c r="V153" t="s">
-        <v>287</v>
-      </c>
-      <c r="W153" t="s">
-        <v>288</v>
+      <c r="V153">
+        <v>93.3333333333333</v>
+      </c>
+      <c r="W153">
+        <v>6.6666666666666696</v>
       </c>
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.3">
@@ -12537,10 +12288,10 @@
         <v>2</v>
       </c>
       <c r="E154" t="s">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="F154" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
       <c r="G154">
         <v>629.84</v>
@@ -12587,11 +12338,11 @@
       <c r="U154">
         <v>0</v>
       </c>
-      <c r="V154" t="s">
-        <v>105</v>
-      </c>
-      <c r="W154" t="s">
-        <v>106</v>
+      <c r="V154">
+        <v>87.5</v>
+      </c>
+      <c r="W154">
+        <v>12.5</v>
       </c>
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.3">
@@ -12608,10 +12359,10 @@
         <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="F155" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="G155">
         <v>416.16300000000001</v>
@@ -12659,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="V155" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W155" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.3">
@@ -12679,10 +12430,10 @@
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>291</v>
+        <v>230</v>
       </c>
       <c r="F156" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="G156">
         <v>103.598</v>
@@ -12730,10 +12481,10 @@
         <v>0</v>
       </c>
       <c r="V156" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W156" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.3">
@@ -12750,10 +12501,10 @@
         <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="F157" t="s">
-        <v>293</v>
+        <v>232</v>
       </c>
       <c r="G157">
         <v>271.584</v>
@@ -12800,11 +12551,11 @@
       <c r="U157">
         <v>2</v>
       </c>
-      <c r="V157" t="s">
-        <v>56</v>
-      </c>
-      <c r="W157" t="s">
-        <v>57</v>
+      <c r="V157">
+        <v>75</v>
+      </c>
+      <c r="W157">
+        <v>25</v>
       </c>
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.3">
@@ -12821,10 +12572,10 @@
         <v>3</v>
       </c>
       <c r="E158" t="s">
-        <v>294</v>
+        <v>233</v>
       </c>
       <c r="F158" t="s">
-        <v>295</v>
+        <v>234</v>
       </c>
       <c r="G158">
         <v>302.63200000000001</v>
@@ -12871,11 +12622,11 @@
       <c r="U158">
         <v>0</v>
       </c>
-      <c r="V158" t="s">
-        <v>29</v>
-      </c>
-      <c r="W158" t="s">
-        <v>30</v>
+      <c r="V158">
+        <v>100</v>
+      </c>
+      <c r="W158">
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:23" x14ac:dyDescent="0.3">
@@ -12892,10 +12643,10 @@
         <v>5</v>
       </c>
       <c r="E159" t="s">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="F159" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="G159">
         <v>455.70600000000002</v>
@@ -12942,11 +12693,11 @@
       <c r="U159">
         <v>0</v>
       </c>
-      <c r="V159" t="s">
-        <v>298</v>
-      </c>
-      <c r="W159" t="s">
-        <v>299</v>
+      <c r="V159">
+        <v>35.714285714285701</v>
+      </c>
+      <c r="W159">
+        <v>64.285714285714207</v>
       </c>
     </row>
     <row r="160" spans="1:23" x14ac:dyDescent="0.3">
@@ -12963,10 +12714,10 @@
         <v>15</v>
       </c>
       <c r="E160" t="s">
-        <v>297</v>
+        <v>236</v>
       </c>
       <c r="F160" t="s">
-        <v>300</v>
+        <v>237</v>
       </c>
       <c r="G160">
         <v>1889.4970000000001</v>
@@ -13013,11 +12764,11 @@
       <c r="U160">
         <v>7</v>
       </c>
-      <c r="V160" t="s">
-        <v>301</v>
-      </c>
-      <c r="W160" t="s">
-        <v>302</v>
+      <c r="V160">
+        <v>61.1111111111111</v>
+      </c>
+      <c r="W160">
+        <v>38.8888888888888</v>
       </c>
     </row>
     <row r="161" spans="1:23" x14ac:dyDescent="0.3">
@@ -13034,10 +12785,10 @@
         <v>6</v>
       </c>
       <c r="E161" t="s">
-        <v>300</v>
+        <v>237</v>
       </c>
       <c r="F161" t="s">
-        <v>303</v>
+        <v>238</v>
       </c>
       <c r="G161">
         <v>1440.1579999999999</v>
@@ -13085,10 +12836,10 @@
         <v>0</v>
       </c>
       <c r="V161" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W161" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:23" x14ac:dyDescent="0.3">
@@ -13105,10 +12856,10 @@
         <v>3</v>
       </c>
       <c r="E162" t="s">
-        <v>304</v>
+        <v>239</v>
       </c>
       <c r="F162" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="G162">
         <v>305.84699999999998</v>
@@ -13155,11 +12906,11 @@
       <c r="U162">
         <v>0</v>
       </c>
-      <c r="V162" t="s">
-        <v>29</v>
-      </c>
-      <c r="W162" t="s">
-        <v>30</v>
+      <c r="V162">
+        <v>100</v>
+      </c>
+      <c r="W162">
+        <v>0</v>
       </c>
     </row>
     <row r="163" spans="1:23" x14ac:dyDescent="0.3">
@@ -13176,10 +12927,10 @@
         <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>305</v>
+        <v>240</v>
       </c>
       <c r="F163" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="G163">
         <v>281.69600000000003</v>
@@ -13227,10 +12978,10 @@
         <v>1</v>
       </c>
       <c r="V163" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W163" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:23" x14ac:dyDescent="0.3">
@@ -13247,10 +12998,10 @@
         <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>306</v>
+        <v>241</v>
       </c>
       <c r="F164" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="G164">
         <v>332</v>
@@ -13298,10 +13049,10 @@
         <v>0</v>
       </c>
       <c r="V164" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W164" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:23" x14ac:dyDescent="0.3">
@@ -13318,10 +13069,10 @@
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>307</v>
+        <v>242</v>
       </c>
       <c r="F165" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="G165">
         <v>242.14500000000001</v>
@@ -13368,11 +13119,11 @@
       <c r="U165">
         <v>0</v>
       </c>
-      <c r="V165" t="s">
-        <v>29</v>
-      </c>
-      <c r="W165" t="s">
-        <v>30</v>
+      <c r="V165">
+        <v>100</v>
+      </c>
+      <c r="W165">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:23" x14ac:dyDescent="0.3">
@@ -13389,10 +13140,10 @@
         <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>308</v>
+        <v>243</v>
       </c>
       <c r="F166" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="G166">
         <v>560.21799999999996</v>
@@ -13439,11 +13190,11 @@
       <c r="U166">
         <v>1</v>
       </c>
-      <c r="V166" t="s">
-        <v>29</v>
-      </c>
-      <c r="W166" t="s">
-        <v>30</v>
+      <c r="V166">
+        <v>100</v>
+      </c>
+      <c r="W166">
+        <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:23" x14ac:dyDescent="0.3">
@@ -13460,10 +13211,10 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>309</v>
+        <v>244</v>
       </c>
       <c r="F167" t="s">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="G167">
         <v>280.65100000000001</v>
@@ -13510,11 +13261,11 @@
       <c r="U167">
         <v>0</v>
       </c>
-      <c r="V167" t="s">
-        <v>56</v>
-      </c>
-      <c r="W167" t="s">
-        <v>57</v>
+      <c r="V167">
+        <v>75</v>
+      </c>
+      <c r="W167">
+        <v>25</v>
       </c>
     </row>
     <row r="168" spans="1:23" x14ac:dyDescent="0.3">
@@ -13531,10 +13282,10 @@
         <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>311</v>
+        <v>246</v>
       </c>
       <c r="F168" t="s">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="G168">
         <v>1901.673</v>
@@ -13581,11 +13332,11 @@
       <c r="U168">
         <v>0</v>
       </c>
-      <c r="V168" t="s">
-        <v>313</v>
-      </c>
-      <c r="W168" t="s">
-        <v>314</v>
+      <c r="V168">
+        <v>69.565217391304301</v>
+      </c>
+      <c r="W168">
+        <v>30.434782608695599</v>
       </c>
     </row>
     <row r="169" spans="1:23" x14ac:dyDescent="0.3">
@@ -13602,10 +13353,10 @@
         <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>312</v>
+        <v>247</v>
       </c>
       <c r="F169" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="G169">
         <v>261.56900000000002</v>
@@ -13652,11 +13403,11 @@
       <c r="U169">
         <v>0</v>
       </c>
-      <c r="V169" t="s">
-        <v>62</v>
-      </c>
-      <c r="W169" t="s">
-        <v>63</v>
+      <c r="V169">
+        <v>85.714285714285694</v>
+      </c>
+      <c r="W169">
+        <v>14.285714285714199</v>
       </c>
     </row>
     <row r="170" spans="1:23" x14ac:dyDescent="0.3">
@@ -13673,10 +13424,10 @@
         <v>6</v>
       </c>
       <c r="E170" t="s">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="F170" t="s">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="G170">
         <v>1938.173</v>
@@ -13723,11 +13474,11 @@
       <c r="U170">
         <v>0</v>
       </c>
-      <c r="V170" t="s">
-        <v>317</v>
-      </c>
-      <c r="W170" t="s">
-        <v>318</v>
+      <c r="V170">
+        <v>93.548387096774107</v>
+      </c>
+      <c r="W170">
+        <v>6.4516129032257998</v>
       </c>
     </row>
     <row r="171" spans="1:23" x14ac:dyDescent="0.3">
@@ -13744,10 +13495,10 @@
         <v>8</v>
       </c>
       <c r="E171" t="s">
-        <v>319</v>
+        <v>250</v>
       </c>
       <c r="F171" t="s">
-        <v>320</v>
+        <v>251</v>
       </c>
       <c r="G171">
         <v>1323.45</v>
@@ -13794,11 +13545,11 @@
       <c r="U171">
         <v>0</v>
       </c>
-      <c r="V171" t="s">
-        <v>321</v>
-      </c>
-      <c r="W171" t="s">
-        <v>322</v>
+      <c r="V171">
+        <v>51.612903225806399</v>
+      </c>
+      <c r="W171">
+        <v>48.387096774193502</v>
       </c>
     </row>
     <row r="172" spans="1:23" x14ac:dyDescent="0.3">
@@ -13815,10 +13566,10 @@
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>320</v>
+        <v>251</v>
       </c>
       <c r="F172" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="G172">
         <v>256.75599999999997</v>
@@ -13865,11 +13616,11 @@
       <c r="U172">
         <v>0</v>
       </c>
-      <c r="V172" t="s">
-        <v>29</v>
-      </c>
-      <c r="W172" t="s">
-        <v>30</v>
+      <c r="V172">
+        <v>100</v>
+      </c>
+      <c r="W172">
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:23" x14ac:dyDescent="0.3">
@@ -13886,10 +13637,10 @@
         <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>323</v>
+        <v>252</v>
       </c>
       <c r="F173" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="G173">
         <v>53.308999999999997</v>
@@ -13937,10 +13688,10 @@
         <v>0</v>
       </c>
       <c r="V173" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W173" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:23" x14ac:dyDescent="0.3">
@@ -13957,10 +13708,10 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="F174" t="s">
-        <v>325</v>
+        <v>254</v>
       </c>
       <c r="G174">
         <v>271.24400000000003</v>
@@ -14007,11 +13758,11 @@
       <c r="U174">
         <v>0</v>
       </c>
-      <c r="V174" t="s">
-        <v>29</v>
-      </c>
-      <c r="W174" t="s">
-        <v>30</v>
+      <c r="V174">
+        <v>100</v>
+      </c>
+      <c r="W174">
+        <v>0</v>
       </c>
     </row>
     <row r="175" spans="1:23" x14ac:dyDescent="0.3">
@@ -14028,10 +13779,10 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="F175" t="s">
-        <v>327</v>
+        <v>256</v>
       </c>
       <c r="G175">
         <v>694.22799999999995</v>
@@ -14078,11 +13829,11 @@
       <c r="U175">
         <v>0</v>
       </c>
-      <c r="V175" t="s">
-        <v>33</v>
-      </c>
-      <c r="W175" t="s">
-        <v>34</v>
+      <c r="V175">
+        <v>77.7777777777777</v>
+      </c>
+      <c r="W175">
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="176" spans="1:23" x14ac:dyDescent="0.3">
@@ -14099,10 +13850,10 @@
         <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>327</v>
+        <v>256</v>
       </c>
       <c r="F176" t="s">
-        <v>328</v>
+        <v>257</v>
       </c>
       <c r="G176">
         <v>524.29200000000003</v>
@@ -14149,11 +13900,11 @@
       <c r="U176">
         <v>0</v>
       </c>
-      <c r="V176" t="s">
-        <v>29</v>
-      </c>
-      <c r="W176" t="s">
-        <v>30</v>
+      <c r="V176">
+        <v>100</v>
+      </c>
+      <c r="W176">
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:23" x14ac:dyDescent="0.3">
@@ -14170,10 +13921,10 @@
         <v>1</v>
       </c>
       <c r="E177" t="s">
-        <v>328</v>
+        <v>257</v>
       </c>
       <c r="F177" t="s">
-        <v>329</v>
+        <v>258</v>
       </c>
       <c r="G177">
         <v>153.41</v>
@@ -14220,11 +13971,11 @@
       <c r="U177">
         <v>0</v>
       </c>
-      <c r="V177" t="s">
-        <v>29</v>
-      </c>
-      <c r="W177" t="s">
-        <v>30</v>
+      <c r="V177">
+        <v>100</v>
+      </c>
+      <c r="W177">
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:23" x14ac:dyDescent="0.3">
@@ -14241,10 +13992,10 @@
         <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>330</v>
+        <v>259</v>
       </c>
       <c r="F178" t="s">
-        <v>331</v>
+        <v>260</v>
       </c>
       <c r="G178">
         <v>495.214</v>
@@ -14291,11 +14042,11 @@
       <c r="U178">
         <v>0</v>
       </c>
-      <c r="V178" t="s">
-        <v>42</v>
-      </c>
-      <c r="W178" t="s">
-        <v>43</v>
+      <c r="V178">
+        <v>90</v>
+      </c>
+      <c r="W178">
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:23" x14ac:dyDescent="0.3">
@@ -14312,10 +14063,10 @@
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>331</v>
+        <v>260</v>
       </c>
       <c r="F179" t="s">
-        <v>332</v>
+        <v>261</v>
       </c>
       <c r="G179">
         <v>253.32900000000001</v>
@@ -14362,11 +14113,11 @@
       <c r="U179">
         <v>1</v>
       </c>
-      <c r="V179" t="s">
-        <v>29</v>
-      </c>
-      <c r="W179" t="s">
-        <v>30</v>
+      <c r="V179">
+        <v>100</v>
+      </c>
+      <c r="W179">
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:23" x14ac:dyDescent="0.3">
@@ -14383,10 +14134,10 @@
         <v>2</v>
       </c>
       <c r="E180" t="s">
-        <v>332</v>
+        <v>261</v>
       </c>
       <c r="F180" t="s">
-        <v>333</v>
+        <v>262</v>
       </c>
       <c r="G180">
         <v>291.51499999999999</v>
@@ -14433,11 +14184,11 @@
       <c r="U180">
         <v>0</v>
       </c>
-      <c r="V180" t="s">
-        <v>334</v>
-      </c>
-      <c r="W180" t="s">
-        <v>335</v>
+      <c r="V180">
+        <v>88.235294117647001</v>
+      </c>
+      <c r="W180">
+        <v>11.764705882352899</v>
       </c>
     </row>
     <row r="181" spans="1:23" x14ac:dyDescent="0.3">
@@ -14454,10 +14205,10 @@
         <v>10</v>
       </c>
       <c r="E181" t="s">
-        <v>336</v>
+        <v>263</v>
       </c>
       <c r="F181" t="s">
-        <v>337</v>
+        <v>264</v>
       </c>
       <c r="G181">
         <v>1945.4490000000001</v>
@@ -14504,11 +14255,11 @@
       <c r="U181">
         <v>0</v>
       </c>
-      <c r="V181" t="s">
-        <v>131</v>
-      </c>
-      <c r="W181" t="s">
-        <v>132</v>
+      <c r="V181">
+        <v>86.6666666666666</v>
+      </c>
+      <c r="W181">
+        <v>13.3333333333333</v>
       </c>
     </row>
     <row r="182" spans="1:23" x14ac:dyDescent="0.3">
@@ -14525,10 +14276,10 @@
         <v>5</v>
       </c>
       <c r="E182" t="s">
-        <v>338</v>
+        <v>265</v>
       </c>
       <c r="F182" t="s">
-        <v>339</v>
+        <v>266</v>
       </c>
       <c r="G182">
         <v>1791.9269999999999</v>
@@ -14575,11 +14326,11 @@
       <c r="U182">
         <v>0</v>
       </c>
-      <c r="V182" t="s">
-        <v>217</v>
-      </c>
-      <c r="W182" t="s">
-        <v>218</v>
+      <c r="V182">
+        <v>81.25</v>
+      </c>
+      <c r="W182">
+        <v>18.75</v>
       </c>
     </row>
     <row r="183" spans="1:23" x14ac:dyDescent="0.3">
@@ -14596,10 +14347,10 @@
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>339</v>
+        <v>266</v>
       </c>
       <c r="F183" t="s">
-        <v>340</v>
+        <v>267</v>
       </c>
       <c r="G183">
         <v>575.88199999999995</v>
@@ -14646,11 +14397,11 @@
       <c r="U183">
         <v>0</v>
       </c>
-      <c r="V183" t="s">
-        <v>29</v>
-      </c>
-      <c r="W183" t="s">
-        <v>30</v>
+      <c r="V183">
+        <v>100</v>
+      </c>
+      <c r="W183">
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:23" x14ac:dyDescent="0.3">
@@ -14667,10 +14418,10 @@
         <v>1</v>
       </c>
       <c r="E184" t="s">
-        <v>340</v>
+        <v>267</v>
       </c>
       <c r="F184" t="s">
-        <v>341</v>
+        <v>268</v>
       </c>
       <c r="G184">
         <v>390.33800000000002</v>
@@ -14717,11 +14468,11 @@
       <c r="U184">
         <v>0</v>
       </c>
-      <c r="V184" t="s">
-        <v>29</v>
-      </c>
-      <c r="W184" t="s">
-        <v>30</v>
+      <c r="V184">
+        <v>100</v>
+      </c>
+      <c r="W184">
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:23" x14ac:dyDescent="0.3">
@@ -14738,10 +14489,10 @@
         <v>5</v>
       </c>
       <c r="E185" t="s">
-        <v>342</v>
+        <v>269</v>
       </c>
       <c r="F185" t="s">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="G185">
         <v>1334.761</v>
@@ -14788,11 +14539,11 @@
       <c r="U185">
         <v>1</v>
       </c>
-      <c r="V185" t="s">
-        <v>102</v>
-      </c>
-      <c r="W185" t="s">
-        <v>101</v>
+      <c r="V185">
+        <v>40</v>
+      </c>
+      <c r="W185">
+        <v>60</v>
       </c>
     </row>
     <row r="186" spans="1:23" x14ac:dyDescent="0.3">
@@ -14809,10 +14560,10 @@
         <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>343</v>
+        <v>270</v>
       </c>
       <c r="F186" t="s">
-        <v>344</v>
+        <v>271</v>
       </c>
       <c r="G186">
         <v>3522.2469999999998</v>
@@ -14859,11 +14610,11 @@
       <c r="U186">
         <v>2</v>
       </c>
-      <c r="V186" t="s">
-        <v>45</v>
-      </c>
-      <c r="W186" t="s">
-        <v>46</v>
+      <c r="V186">
+        <v>83.3333333333333</v>
+      </c>
+      <c r="W186">
+        <v>16.6666666666666</v>
       </c>
     </row>
     <row r="187" spans="1:23" x14ac:dyDescent="0.3">
@@ -14880,10 +14631,10 @@
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>345</v>
+        <v>272</v>
       </c>
       <c r="F187" t="s">
-        <v>346</v>
+        <v>273</v>
       </c>
       <c r="G187">
         <v>136.62299999999999</v>
@@ -14930,11 +14681,11 @@
       <c r="U187">
         <v>0</v>
       </c>
-      <c r="V187" t="s">
-        <v>29</v>
-      </c>
-      <c r="W187" t="s">
-        <v>30</v>
+      <c r="V187">
+        <v>100</v>
+      </c>
+      <c r="W187">
+        <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:23" x14ac:dyDescent="0.3">
@@ -14951,10 +14702,10 @@
         <v>11</v>
       </c>
       <c r="E188" t="s">
-        <v>347</v>
+        <v>274</v>
       </c>
       <c r="F188" t="s">
-        <v>348</v>
+        <v>275</v>
       </c>
       <c r="G188">
         <v>1212.942</v>
@@ -15001,11 +14752,11 @@
       <c r="U188">
         <v>0</v>
       </c>
-      <c r="V188" t="s">
-        <v>56</v>
-      </c>
-      <c r="W188" t="s">
-        <v>57</v>
+      <c r="V188">
+        <v>75</v>
+      </c>
+      <c r="W188">
+        <v>25</v>
       </c>
     </row>
     <row r="189" spans="1:23" x14ac:dyDescent="0.3">
@@ -15022,10 +14773,10 @@
         <v>3</v>
       </c>
       <c r="E189" t="s">
-        <v>349</v>
+        <v>276</v>
       </c>
       <c r="F189" t="s">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="G189">
         <v>439.37299999999999</v>
@@ -15072,11 +14823,11 @@
       <c r="U189">
         <v>0</v>
       </c>
-      <c r="V189" t="s">
-        <v>162</v>
-      </c>
-      <c r="W189" t="s">
-        <v>163</v>
+      <c r="V189">
+        <v>90.909090909090907</v>
+      </c>
+      <c r="W189">
+        <v>9.0909090909090899</v>
       </c>
     </row>
     <row r="190" spans="1:23" x14ac:dyDescent="0.3">
@@ -15093,10 +14844,10 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="F190" t="s">
-        <v>351</v>
+        <v>278</v>
       </c>
       <c r="G190">
         <v>145.673</v>
@@ -15143,11 +14894,11 @@
       <c r="U190">
         <v>1</v>
       </c>
-      <c r="V190" t="s">
-        <v>29</v>
-      </c>
-      <c r="W190" t="s">
-        <v>30</v>
+      <c r="V190">
+        <v>100</v>
+      </c>
+      <c r="W190">
+        <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:23" x14ac:dyDescent="0.3">
@@ -15164,10 +14915,10 @@
         <v>2</v>
       </c>
       <c r="E191" t="s">
-        <v>352</v>
+        <v>279</v>
       </c>
       <c r="F191" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="G191">
         <v>264.03100000000001</v>
@@ -15214,11 +14965,11 @@
       <c r="U191">
         <v>0</v>
       </c>
-      <c r="V191" t="s">
-        <v>62</v>
-      </c>
-      <c r="W191" t="s">
-        <v>63</v>
+      <c r="V191">
+        <v>85.714285714285694</v>
+      </c>
+      <c r="W191">
+        <v>14.285714285714199</v>
       </c>
     </row>
     <row r="192" spans="1:23" x14ac:dyDescent="0.3">
@@ -15235,10 +14986,10 @@
         <v>2</v>
       </c>
       <c r="E192" t="s">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="F192" t="s">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="G192">
         <v>293.161</v>
@@ -15285,11 +15036,11 @@
       <c r="U192">
         <v>0</v>
       </c>
-      <c r="V192" t="s">
-        <v>29</v>
-      </c>
-      <c r="W192" t="s">
-        <v>30</v>
+      <c r="V192">
+        <v>100</v>
+      </c>
+      <c r="W192">
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:23" x14ac:dyDescent="0.3">
@@ -15306,10 +15057,10 @@
         <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="F193" t="s">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="G193">
         <v>166.51599999999999</v>
@@ -15356,11 +15107,11 @@
       <c r="U193">
         <v>0</v>
       </c>
-      <c r="V193" t="s">
-        <v>29</v>
-      </c>
-      <c r="W193" t="s">
-        <v>30</v>
+      <c r="V193">
+        <v>100</v>
+      </c>
+      <c r="W193">
+        <v>0</v>
       </c>
     </row>
     <row r="194" spans="1:23" x14ac:dyDescent="0.3">
@@ -15377,10 +15128,10 @@
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="F194" t="s">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="G194">
         <v>178.62299999999999</v>
@@ -15427,11 +15178,11 @@
       <c r="U194">
         <v>0</v>
       </c>
-      <c r="V194" t="s">
-        <v>29</v>
-      </c>
-      <c r="W194" t="s">
-        <v>30</v>
+      <c r="V194">
+        <v>100</v>
+      </c>
+      <c r="W194">
+        <v>0</v>
       </c>
     </row>
     <row r="195" spans="1:23" x14ac:dyDescent="0.3">
@@ -15448,10 +15199,10 @@
         <v>3</v>
       </c>
       <c r="E195" t="s">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="F195" t="s">
-        <v>357</v>
+        <v>284</v>
       </c>
       <c r="G195">
         <v>300.98700000000002</v>
@@ -15498,11 +15249,11 @@
       <c r="U195">
         <v>0</v>
       </c>
-      <c r="V195" t="s">
-        <v>29</v>
-      </c>
-      <c r="W195" t="s">
-        <v>30</v>
+      <c r="V195">
+        <v>100</v>
+      </c>
+      <c r="W195">
+        <v>0</v>
       </c>
     </row>
     <row r="196" spans="1:23" x14ac:dyDescent="0.3">
@@ -15519,10 +15270,10 @@
         <v>2</v>
       </c>
       <c r="E196" t="s">
-        <v>358</v>
+        <v>285</v>
       </c>
       <c r="F196" t="s">
-        <v>359</v>
+        <v>286</v>
       </c>
       <c r="G196">
         <v>363.834</v>
@@ -15570,10 +15321,10 @@
         <v>0</v>
       </c>
       <c r="V196" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W196" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197" spans="1:23" x14ac:dyDescent="0.3">
@@ -15590,10 +15341,10 @@
         <v>2</v>
       </c>
       <c r="E197" t="s">
-        <v>359</v>
+        <v>286</v>
       </c>
       <c r="F197" t="s">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="G197">
         <v>306.89299999999997</v>
@@ -15641,10 +15392,10 @@
         <v>0</v>
       </c>
       <c r="V197" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W197" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="198" spans="1:23" x14ac:dyDescent="0.3">
@@ -15661,10 +15412,10 @@
         <v>1</v>
       </c>
       <c r="E198" t="s">
-        <v>360</v>
+        <v>287</v>
       </c>
       <c r="F198" t="s">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="G198">
         <v>43.689</v>
@@ -15712,10 +15463,10 @@
         <v>0</v>
       </c>
       <c r="V198" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W198" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199" spans="1:23" x14ac:dyDescent="0.3">
@@ -15732,10 +15483,10 @@
         <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="F199" t="s">
-        <v>362</v>
+        <v>289</v>
       </c>
       <c r="G199">
         <v>204.87799999999999</v>
@@ -15782,11 +15533,11 @@
       <c r="U199">
         <v>1</v>
       </c>
-      <c r="V199" t="s">
-        <v>188</v>
-      </c>
-      <c r="W199" t="s">
-        <v>189</v>
+      <c r="V199">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W199">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="200" spans="1:23" x14ac:dyDescent="0.3">
@@ -15803,10 +15554,10 @@
         <v>1</v>
       </c>
       <c r="E200" t="s">
-        <v>363</v>
+        <v>290</v>
       </c>
       <c r="F200" t="s">
-        <v>364</v>
+        <v>291</v>
       </c>
       <c r="G200">
         <v>33.176000000000002</v>
@@ -15854,10 +15605,10 @@
         <v>0</v>
       </c>
       <c r="V200" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W200" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="201" spans="1:23" x14ac:dyDescent="0.3">
@@ -15874,10 +15625,10 @@
         <v>7</v>
       </c>
       <c r="E201" t="s">
-        <v>365</v>
+        <v>292</v>
       </c>
       <c r="F201" t="s">
-        <v>366</v>
+        <v>293</v>
       </c>
       <c r="G201">
         <v>1414.277</v>
@@ -15924,11 +15675,11 @@
       <c r="U201">
         <v>0</v>
       </c>
-      <c r="V201" t="s">
-        <v>367</v>
-      </c>
-      <c r="W201" t="s">
-        <v>368</v>
+      <c r="V201">
+        <v>75.862068965517196</v>
+      </c>
+      <c r="W201">
+        <v>24.137931034482701</v>
       </c>
     </row>
     <row r="202" spans="1:23" x14ac:dyDescent="0.3">
@@ -15945,10 +15696,10 @@
         <v>1</v>
       </c>
       <c r="E202" t="s">
-        <v>366</v>
+        <v>293</v>
       </c>
       <c r="F202" t="s">
-        <v>369</v>
+        <v>294</v>
       </c>
       <c r="G202">
         <v>236.52099999999999</v>
@@ -15996,10 +15747,10 @@
         <v>0</v>
       </c>
       <c r="V202" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W202" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="203" spans="1:23" x14ac:dyDescent="0.3">
@@ -16016,10 +15767,10 @@
         <v>1</v>
       </c>
       <c r="E203" t="s">
-        <v>369</v>
+        <v>294</v>
       </c>
       <c r="F203" t="s">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="G203">
         <v>3.0000000000000001E-3</v>
@@ -16067,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="V203" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W203" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="204" spans="1:23" x14ac:dyDescent="0.3">
@@ -16087,10 +15838,10 @@
         <v>3</v>
       </c>
       <c r="E204" t="s">
-        <v>371</v>
+        <v>296</v>
       </c>
       <c r="F204" t="s">
-        <v>372</v>
+        <v>297</v>
       </c>
       <c r="G204">
         <v>521.17200000000003</v>
@@ -16138,10 +15889,10 @@
         <v>0</v>
       </c>
       <c r="V204" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W204" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="205" spans="1:23" x14ac:dyDescent="0.3">
@@ -16158,10 +15909,10 @@
         <v>2</v>
       </c>
       <c r="E205" t="s">
-        <v>372</v>
+        <v>297</v>
       </c>
       <c r="F205" t="s">
-        <v>373</v>
+        <v>298</v>
       </c>
       <c r="G205">
         <v>458.50900000000001</v>
@@ -16209,10 +15960,10 @@
         <v>0</v>
       </c>
       <c r="V205" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="W205" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="206" spans="1:23" x14ac:dyDescent="0.3">
@@ -16229,10 +15980,10 @@
         <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>374</v>
+        <v>299</v>
       </c>
       <c r="F206" t="s">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="G206">
         <v>1146.846</v>
@@ -16279,11 +16030,11 @@
       <c r="U206">
         <v>0</v>
       </c>
-      <c r="V206" t="s">
-        <v>178</v>
-      </c>
-      <c r="W206" t="s">
-        <v>179</v>
+      <c r="V206">
+        <v>71.428571428571402</v>
+      </c>
+      <c r="W206">
+        <v>28.571428571428498</v>
       </c>
     </row>
     <row r="207" spans="1:23" x14ac:dyDescent="0.3">
@@ -16300,10 +16051,10 @@
         <v>13</v>
       </c>
       <c r="E207" t="s">
-        <v>376</v>
+        <v>301</v>
       </c>
       <c r="F207" t="s">
-        <v>377</v>
+        <v>302</v>
       </c>
       <c r="G207">
         <v>2677.895</v>
@@ -16350,11 +16101,11 @@
       <c r="U207">
         <v>2</v>
       </c>
-      <c r="V207" t="s">
-        <v>378</v>
-      </c>
-      <c r="W207" t="s">
-        <v>379</v>
+      <c r="V207">
+        <v>76</v>
+      </c>
+      <c r="W207">
+        <v>24</v>
       </c>
     </row>
     <row r="208" spans="1:23" x14ac:dyDescent="0.3">
@@ -16371,10 +16122,10 @@
         <v>7</v>
       </c>
       <c r="E208" t="s">
-        <v>380</v>
+        <v>303</v>
       </c>
       <c r="F208" t="s">
-        <v>381</v>
+        <v>304</v>
       </c>
       <c r="G208">
         <v>1421.896</v>
@@ -16421,11 +16172,11 @@
       <c r="U208">
         <v>0</v>
       </c>
-      <c r="V208" t="s">
-        <v>382</v>
-      </c>
-      <c r="W208" t="s">
-        <v>383</v>
+      <c r="V208">
+        <v>93.75</v>
+      </c>
+      <c r="W208">
+        <v>6.25</v>
       </c>
     </row>
     <row r="209" spans="1:23" x14ac:dyDescent="0.3">
@@ -16442,10 +16193,10 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>381</v>
+        <v>304</v>
       </c>
       <c r="F209" t="s">
-        <v>384</v>
+        <v>305</v>
       </c>
       <c r="G209">
         <v>379.99400000000003</v>
@@ -16492,11 +16243,11 @@
       <c r="U209">
         <v>0</v>
       </c>
-      <c r="V209" t="s">
-        <v>29</v>
-      </c>
-      <c r="W209" t="s">
-        <v>30</v>
+      <c r="V209">
+        <v>100</v>
+      </c>
+      <c r="W209">
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:23" x14ac:dyDescent="0.3">
@@ -16513,10 +16264,10 @@
         <v>4</v>
       </c>
       <c r="E210" t="s">
-        <v>384</v>
+        <v>305</v>
       </c>
       <c r="F210" t="s">
-        <v>385</v>
+        <v>306</v>
       </c>
       <c r="G210">
         <v>284.67899999999997</v>
@@ -16563,11 +16314,11 @@
       <c r="U210">
         <v>0</v>
       </c>
-      <c r="V210" t="s">
-        <v>188</v>
-      </c>
-      <c r="W210" t="s">
-        <v>189</v>
+      <c r="V210">
+        <v>66.6666666666666</v>
+      </c>
+      <c r="W210">
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="211" spans="1:23" x14ac:dyDescent="0.3">
@@ -16584,10 +16335,10 @@
         <v>5</v>
       </c>
       <c r="E211" t="s">
-        <v>386</v>
+        <v>307</v>
       </c>
       <c r="F211" t="s">
-        <v>387</v>
+        <v>308</v>
       </c>
       <c r="G211">
         <v>679.69</v>
@@ -16634,11 +16385,11 @@
       <c r="U211">
         <v>0</v>
       </c>
-      <c r="V211" t="s">
-        <v>388</v>
-      </c>
-      <c r="W211" t="s">
-        <v>389</v>
+      <c r="V211">
+        <v>64.285714285714207</v>
+      </c>
+      <c r="W211">
+        <v>35.714285714285701</v>
       </c>
     </row>
     <row r="212" spans="1:23" x14ac:dyDescent="0.3">
@@ -16655,10 +16406,10 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>387</v>
+        <v>308</v>
       </c>
       <c r="F212" t="s">
-        <v>390</v>
+        <v>309</v>
       </c>
       <c r="G212">
         <v>235.70599999999999</v>
@@ -16705,11 +16456,11 @@
       <c r="U212">
         <v>0</v>
       </c>
-      <c r="V212" t="s">
-        <v>29</v>
-      </c>
-      <c r="W212" t="s">
-        <v>30</v>
+      <c r="V212">
+        <v>100</v>
+      </c>
+      <c r="W212">
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:23" x14ac:dyDescent="0.3">
@@ -16726,10 +16477,10 @@
         <v>4</v>
       </c>
       <c r="E213" t="s">
-        <v>390</v>
+        <v>309</v>
       </c>
       <c r="F213" t="s">
-        <v>391</v>
+        <v>310</v>
       </c>
       <c r="G213">
         <v>825.14700000000005</v>
@@ -16776,11 +16527,11 @@
       <c r="U213">
         <v>0</v>
       </c>
-      <c r="V213" t="s">
-        <v>392</v>
-      </c>
-      <c r="W213" t="s">
-        <v>393</v>
+      <c r="V213">
+        <v>82.352941176470594</v>
+      </c>
+      <c r="W213">
+        <v>17.647058823529399</v>
       </c>
     </row>
   </sheetData>
